--- a/tests/data/20250305_experiment_file.xlsx
+++ b/tests/data/20250305_experiment_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Desktop-PC\PycharmProjects\nomad-hysprint\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17323FD9-1895-4553-A1C8-3DBC035C9993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB17D7A1-13D6-433B-8F34-5988C92EB259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="163">
   <si>
     <t>Experiment Info</t>
   </si>
@@ -426,9 +426,6 @@
   </si>
   <si>
     <t>1000 rpm</t>
-  </si>
-  <si>
-    <t>1 cm x 1 cm</t>
   </si>
   <si>
     <t>Glass</t>
@@ -2110,8 +2107,9 @@
       <c r="G3" t="s">
         <v>130</v>
       </c>
-      <c r="H3" t="s">
-        <v>131</v>
+      <c r="H3">
+        <f>2.5*2.5</f>
+        <v>6.25</v>
       </c>
       <c r="I3">
         <v>0.16</v>
@@ -2123,19 +2121,19 @@
         <v>0.16</v>
       </c>
       <c r="L3" t="s">
+        <v>131</v>
+      </c>
+      <c r="M3" t="s">
         <v>132</v>
-      </c>
-      <c r="M3" t="s">
-        <v>133</v>
       </c>
       <c r="N3">
         <v>1</v>
       </c>
       <c r="O3" t="s">
+        <v>133</v>
+      </c>
+      <c r="P3" t="s">
         <v>134</v>
-      </c>
-      <c r="P3" t="s">
-        <v>135</v>
       </c>
       <c r="Q3">
         <v>31</v>
@@ -2144,7 +2142,7 @@
         <v>61</v>
       </c>
       <c r="S3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T3">
         <v>32</v>
@@ -2153,7 +2151,7 @@
         <v>62</v>
       </c>
       <c r="V3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W3">
         <v>180</v>
@@ -2162,7 +2160,7 @@
         <v>50</v>
       </c>
       <c r="Y3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z3">
         <v>31</v>
@@ -2171,7 +2169,7 @@
         <v>61</v>
       </c>
       <c r="AB3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC3">
         <v>32</v>
@@ -2183,16 +2181,16 @@
         <v>900</v>
       </c>
       <c r="AF3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG3" t="s">
         <v>137</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AH3" t="s">
         <v>138</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AI3" t="s">
         <v>139</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>140</v>
       </c>
       <c r="AJ3">
         <v>10</v>
@@ -2201,7 +2199,7 @@
         <v>1.5</v>
       </c>
       <c r="AL3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AM3">
         <v>1.42</v>
@@ -2228,22 +2226,22 @@
         <v>120</v>
       </c>
       <c r="AU3" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV3" t="s">
         <v>142</v>
       </c>
-      <c r="AV3" t="s">
-        <v>143</v>
-      </c>
       <c r="AW3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX3" t="s">
         <v>137</v>
       </c>
-      <c r="AX3" t="s">
+      <c r="AY3" t="s">
         <v>138</v>
       </c>
-      <c r="AY3" t="s">
+      <c r="AZ3" t="s">
         <v>139</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>140</v>
       </c>
       <c r="BA3">
         <v>10</v>
@@ -2252,7 +2250,7 @@
         <v>1.5</v>
       </c>
       <c r="BC3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD3">
         <v>20</v>
@@ -2261,31 +2259,31 @@
         <v>1.5</v>
       </c>
       <c r="BF3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BG3">
         <v>1.42</v>
       </c>
       <c r="BH3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI3">
         <v>1.42</v>
       </c>
       <c r="BJ3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK3">
         <v>1.42</v>
       </c>
       <c r="BL3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BM3">
         <v>1.42</v>
       </c>
       <c r="BN3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BO3">
         <v>1.42</v>
@@ -2300,22 +2298,22 @@
         <v>120</v>
       </c>
       <c r="BS3" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT3" t="s">
         <v>142</v>
       </c>
-      <c r="BT3" t="s">
-        <v>143</v>
-      </c>
       <c r="BU3" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV3" t="s">
         <v>137</v>
       </c>
-      <c r="BV3" t="s">
+      <c r="BW3" t="s">
         <v>138</v>
       </c>
-      <c r="BW3" t="s">
+      <c r="BX3" t="s">
         <v>139</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>140</v>
       </c>
       <c r="BY3">
         <v>10</v>
@@ -2324,13 +2322,13 @@
         <v>1.5</v>
       </c>
       <c r="CA3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CB3">
         <v>1.42</v>
       </c>
       <c r="CC3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CD3">
         <v>1.42</v>
@@ -2366,22 +2364,22 @@
         <v>120</v>
       </c>
       <c r="CO3" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP3" t="s">
         <v>142</v>
       </c>
-      <c r="CP3" t="s">
-        <v>143</v>
-      </c>
       <c r="CQ3" t="s">
+        <v>136</v>
+      </c>
+      <c r="CR3" t="s">
         <v>137</v>
       </c>
-      <c r="CR3" t="s">
+      <c r="CS3" t="s">
         <v>138</v>
       </c>
-      <c r="CS3" t="s">
+      <c r="CT3" t="s">
         <v>139</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>140</v>
       </c>
       <c r="CU3">
         <v>10</v>
@@ -2390,19 +2388,19 @@
         <v>1.5</v>
       </c>
       <c r="CW3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CX3">
         <v>1.42</v>
       </c>
       <c r="CY3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CZ3">
         <v>1.42</v>
       </c>
       <c r="DA3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="DB3">
         <v>128</v>
@@ -2444,19 +2442,19 @@
         <v>120</v>
       </c>
       <c r="DO3" t="s">
+        <v>141</v>
+      </c>
+      <c r="DP3" t="s">
         <v>142</v>
       </c>
-      <c r="DP3" t="s">
-        <v>143</v>
-      </c>
       <c r="DQ3" t="s">
+        <v>144</v>
+      </c>
+      <c r="DR3" t="s">
         <v>145</v>
       </c>
-      <c r="DR3" t="s">
+      <c r="DS3" t="s">
         <v>146</v>
-      </c>
-      <c r="DS3" t="s">
-        <v>147</v>
       </c>
       <c r="DT3" t="b">
         <v>1</v>
@@ -2492,16 +2490,16 @@
         <v>1.5</v>
       </c>
       <c r="EE3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="EF3" t="s">
+        <v>144</v>
+      </c>
+      <c r="EG3" t="s">
         <v>145</v>
       </c>
-      <c r="EG3" t="s">
+      <c r="EH3" t="s">
         <v>146</v>
-      </c>
-      <c r="EH3" t="s">
-        <v>147</v>
       </c>
       <c r="EI3" t="b">
         <v>0</v>
@@ -2537,16 +2535,16 @@
         <v>1.5</v>
       </c>
       <c r="ET3" t="s">
+        <v>147</v>
+      </c>
+      <c r="EU3" t="s">
         <v>148</v>
       </c>
-      <c r="EU3" t="s">
+      <c r="EV3" t="s">
         <v>149</v>
       </c>
-      <c r="EV3" t="s">
+      <c r="EW3" t="s">
         <v>150</v>
-      </c>
-      <c r="EW3" t="s">
-        <v>151</v>
       </c>
       <c r="EX3">
         <v>9.9999999999999995E-7</v>
@@ -2561,13 +2559,13 @@
         <v>25</v>
       </c>
       <c r="FB3" t="s">
+        <v>148</v>
+      </c>
+      <c r="FC3" t="s">
         <v>149</v>
       </c>
-      <c r="FC3" t="s">
+      <c r="FD3" t="s">
         <v>150</v>
-      </c>
-      <c r="FD3" t="s">
-        <v>151</v>
       </c>
       <c r="FE3">
         <v>9.9999999999999995E-7</v>
@@ -2582,16 +2580,16 @@
         <v>25</v>
       </c>
       <c r="FI3" t="s">
+        <v>151</v>
+      </c>
+      <c r="FJ3" t="s">
+        <v>145</v>
+      </c>
+      <c r="FK3" t="s">
         <v>152</v>
       </c>
-      <c r="FJ3" t="s">
-        <v>146</v>
-      </c>
-      <c r="FK3" t="s">
+      <c r="FL3" t="s">
         <v>153</v>
-      </c>
-      <c r="FL3" t="s">
-        <v>154</v>
       </c>
       <c r="FM3">
         <v>200</v>
@@ -2618,7 +2616,7 @@
         <v>20</v>
       </c>
       <c r="FU3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="FV3">
         <v>532</v>
@@ -2639,19 +2637,19 @@
         <v>75</v>
       </c>
       <c r="GB3" t="s">
+        <v>155</v>
+      </c>
+      <c r="GC3" t="s">
         <v>156</v>
       </c>
-      <c r="GC3" t="s">
+      <c r="GD3" t="s">
+        <v>145</v>
+      </c>
+      <c r="GE3" t="s">
         <v>157</v>
       </c>
-      <c r="GD3" t="s">
-        <v>146</v>
-      </c>
-      <c r="GE3" t="s">
+      <c r="GF3" t="s">
         <v>158</v>
-      </c>
-      <c r="GF3" t="s">
-        <v>159</v>
       </c>
       <c r="GG3">
         <v>25</v>
@@ -2669,7 +2667,7 @@
         <v>250</v>
       </c>
       <c r="GL3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="GM3">
         <v>0.2</v>
@@ -2681,7 +2679,7 @@
         <v>25</v>
       </c>
       <c r="GP3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="GQ3">
         <v>0.1</v>
@@ -2696,19 +2694,19 @@
         <v>150</v>
       </c>
       <c r="GU3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="GV3">
         <v>35</v>
       </c>
       <c r="GW3" t="s">
+        <v>160</v>
+      </c>
+      <c r="GX3" t="s">
         <v>161</v>
       </c>
-      <c r="GX3" t="s">
+      <c r="GY3" t="s">
         <v>162</v>
-      </c>
-      <c r="GY3" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:207" x14ac:dyDescent="0.3">
@@ -2734,8 +2732,9 @@
       <c r="G4" t="s">
         <v>130</v>
       </c>
-      <c r="H4" t="s">
-        <v>131</v>
+      <c r="H4">
+        <f t="shared" ref="H4:H18" si="1">2.5*2.5</f>
+        <v>6.25</v>
       </c>
       <c r="I4">
         <v>0.16</v>
@@ -2747,19 +2746,19 @@
         <v>0.16</v>
       </c>
       <c r="L4" t="s">
+        <v>131</v>
+      </c>
+      <c r="M4" t="s">
         <v>132</v>
-      </c>
-      <c r="M4" t="s">
-        <v>133</v>
       </c>
       <c r="N4">
         <v>1</v>
       </c>
       <c r="O4" t="s">
+        <v>133</v>
+      </c>
+      <c r="P4" t="s">
         <v>134</v>
-      </c>
-      <c r="P4" t="s">
-        <v>135</v>
       </c>
       <c r="Q4">
         <v>31</v>
@@ -2768,7 +2767,7 @@
         <v>61</v>
       </c>
       <c r="S4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T4">
         <v>32</v>
@@ -2777,7 +2776,7 @@
         <v>62</v>
       </c>
       <c r="V4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W4">
         <v>180</v>
@@ -2786,7 +2785,7 @@
         <v>50</v>
       </c>
       <c r="Y4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z4">
         <v>31</v>
@@ -2795,7 +2794,7 @@
         <v>61</v>
       </c>
       <c r="AB4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC4">
         <v>32</v>
@@ -2807,16 +2806,16 @@
         <v>900</v>
       </c>
       <c r="AF4" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG4" t="s">
         <v>137</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>138</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>139</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>140</v>
       </c>
       <c r="AJ4">
         <v>10</v>
@@ -2825,7 +2824,7 @@
         <v>1.5</v>
       </c>
       <c r="AL4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AM4">
         <v>1.42</v>
@@ -2852,22 +2851,22 @@
         <v>120</v>
       </c>
       <c r="AU4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV4" t="s">
         <v>142</v>
       </c>
-      <c r="AV4" t="s">
-        <v>143</v>
-      </c>
       <c r="AW4" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX4" t="s">
         <v>137</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>138</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>139</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>140</v>
       </c>
       <c r="BA4">
         <v>10</v>
@@ -2876,7 +2875,7 @@
         <v>1.5</v>
       </c>
       <c r="BC4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD4">
         <v>20</v>
@@ -2885,31 +2884,31 @@
         <v>1.5</v>
       </c>
       <c r="BF4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BG4">
         <v>1.42</v>
       </c>
       <c r="BH4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI4">
         <v>1.42</v>
       </c>
       <c r="BJ4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK4">
         <v>1.42</v>
       </c>
       <c r="BL4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BM4">
         <v>1.42</v>
       </c>
       <c r="BN4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BO4">
         <v>1.42</v>
@@ -2924,22 +2923,22 @@
         <v>120</v>
       </c>
       <c r="BS4" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT4" t="s">
         <v>142</v>
       </c>
-      <c r="BT4" t="s">
-        <v>143</v>
-      </c>
       <c r="BU4" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV4" t="s">
         <v>137</v>
       </c>
-      <c r="BV4" t="s">
+      <c r="BW4" t="s">
         <v>138</v>
       </c>
-      <c r="BW4" t="s">
+      <c r="BX4" t="s">
         <v>139</v>
-      </c>
-      <c r="BX4" t="s">
-        <v>140</v>
       </c>
       <c r="BY4">
         <v>10</v>
@@ -2948,13 +2947,13 @@
         <v>1.5</v>
       </c>
       <c r="CA4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CB4">
         <v>1.42</v>
       </c>
       <c r="CC4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CD4">
         <v>1.42</v>
@@ -2990,22 +2989,22 @@
         <v>120</v>
       </c>
       <c r="CO4" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP4" t="s">
         <v>142</v>
       </c>
-      <c r="CP4" t="s">
-        <v>143</v>
-      </c>
       <c r="CQ4" t="s">
+        <v>136</v>
+      </c>
+      <c r="CR4" t="s">
         <v>137</v>
       </c>
-      <c r="CR4" t="s">
+      <c r="CS4" t="s">
         <v>138</v>
       </c>
-      <c r="CS4" t="s">
+      <c r="CT4" t="s">
         <v>139</v>
-      </c>
-      <c r="CT4" t="s">
-        <v>140</v>
       </c>
       <c r="CU4">
         <v>10</v>
@@ -3014,19 +3013,19 @@
         <v>1.5</v>
       </c>
       <c r="CW4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CX4">
         <v>1.42</v>
       </c>
       <c r="CY4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CZ4">
         <v>1.42</v>
       </c>
       <c r="DA4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="DB4">
         <v>128</v>
@@ -3068,19 +3067,19 @@
         <v>120</v>
       </c>
       <c r="DO4" t="s">
+        <v>141</v>
+      </c>
+      <c r="DP4" t="s">
         <v>142</v>
       </c>
-      <c r="DP4" t="s">
-        <v>143</v>
-      </c>
       <c r="DQ4" t="s">
+        <v>144</v>
+      </c>
+      <c r="DR4" t="s">
         <v>145</v>
       </c>
-      <c r="DR4" t="s">
+      <c r="DS4" t="s">
         <v>146</v>
-      </c>
-      <c r="DS4" t="s">
-        <v>147</v>
       </c>
       <c r="DT4" t="b">
         <v>1</v>
@@ -3116,16 +3115,16 @@
         <v>1.5</v>
       </c>
       <c r="EE4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="EF4" t="s">
+        <v>144</v>
+      </c>
+      <c r="EG4" t="s">
         <v>145</v>
       </c>
-      <c r="EG4" t="s">
+      <c r="EH4" t="s">
         <v>146</v>
-      </c>
-      <c r="EH4" t="s">
-        <v>147</v>
       </c>
       <c r="EI4" t="b">
         <v>0</v>
@@ -3161,16 +3160,16 @@
         <v>1.5</v>
       </c>
       <c r="ET4" t="s">
+        <v>147</v>
+      </c>
+      <c r="EU4" t="s">
         <v>148</v>
       </c>
-      <c r="EU4" t="s">
+      <c r="EV4" t="s">
         <v>149</v>
       </c>
-      <c r="EV4" t="s">
+      <c r="EW4" t="s">
         <v>150</v>
-      </c>
-      <c r="EW4" t="s">
-        <v>151</v>
       </c>
       <c r="EX4">
         <v>9.9999999999999995E-7</v>
@@ -3185,13 +3184,13 @@
         <v>25</v>
       </c>
       <c r="FB4" t="s">
+        <v>148</v>
+      </c>
+      <c r="FC4" t="s">
         <v>149</v>
       </c>
-      <c r="FC4" t="s">
+      <c r="FD4" t="s">
         <v>150</v>
-      </c>
-      <c r="FD4" t="s">
-        <v>151</v>
       </c>
       <c r="FE4">
         <v>9.9999999999999995E-7</v>
@@ -3206,16 +3205,16 @@
         <v>25</v>
       </c>
       <c r="FI4" t="s">
+        <v>151</v>
+      </c>
+      <c r="FJ4" t="s">
+        <v>145</v>
+      </c>
+      <c r="FK4" t="s">
         <v>152</v>
       </c>
-      <c r="FJ4" t="s">
-        <v>146</v>
-      </c>
-      <c r="FK4" t="s">
+      <c r="FL4" t="s">
         <v>153</v>
-      </c>
-      <c r="FL4" t="s">
-        <v>154</v>
       </c>
       <c r="FM4">
         <v>200</v>
@@ -3242,7 +3241,7 @@
         <v>20</v>
       </c>
       <c r="FU4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="FV4">
         <v>532</v>
@@ -3263,19 +3262,19 @@
         <v>75</v>
       </c>
       <c r="GB4" t="s">
+        <v>155</v>
+      </c>
+      <c r="GC4" t="s">
         <v>156</v>
       </c>
-      <c r="GC4" t="s">
+      <c r="GD4" t="s">
+        <v>145</v>
+      </c>
+      <c r="GE4" t="s">
         <v>157</v>
       </c>
-      <c r="GD4" t="s">
-        <v>146</v>
-      </c>
-      <c r="GE4" t="s">
+      <c r="GF4" t="s">
         <v>158</v>
-      </c>
-      <c r="GF4" t="s">
-        <v>159</v>
       </c>
       <c r="GG4">
         <v>25</v>
@@ -3293,7 +3292,7 @@
         <v>250</v>
       </c>
       <c r="GL4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="GM4">
         <v>0.2</v>
@@ -3305,7 +3304,7 @@
         <v>25</v>
       </c>
       <c r="GP4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="GQ4">
         <v>0.1</v>
@@ -3320,19 +3319,19 @@
         <v>150</v>
       </c>
       <c r="GU4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="GV4">
         <v>35</v>
       </c>
       <c r="GW4" t="s">
+        <v>160</v>
+      </c>
+      <c r="GX4" t="s">
         <v>161</v>
       </c>
-      <c r="GX4" t="s">
+      <c r="GY4" t="s">
         <v>162</v>
-      </c>
-      <c r="GY4" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:207" x14ac:dyDescent="0.3">
@@ -3358,8 +3357,9 @@
       <c r="G5" t="s">
         <v>130</v>
       </c>
-      <c r="H5" t="s">
-        <v>131</v>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>6.25</v>
       </c>
       <c r="I5">
         <v>0.16</v>
@@ -3371,19 +3371,19 @@
         <v>0.16</v>
       </c>
       <c r="L5" t="s">
+        <v>131</v>
+      </c>
+      <c r="M5" t="s">
         <v>132</v>
-      </c>
-      <c r="M5" t="s">
-        <v>133</v>
       </c>
       <c r="N5">
         <v>1</v>
       </c>
       <c r="O5" t="s">
+        <v>133</v>
+      </c>
+      <c r="P5" t="s">
         <v>134</v>
-      </c>
-      <c r="P5" t="s">
-        <v>135</v>
       </c>
       <c r="Q5">
         <v>31</v>
@@ -3392,7 +3392,7 @@
         <v>61</v>
       </c>
       <c r="S5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T5">
         <v>32</v>
@@ -3401,7 +3401,7 @@
         <v>62</v>
       </c>
       <c r="V5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W5">
         <v>180</v>
@@ -3410,7 +3410,7 @@
         <v>50</v>
       </c>
       <c r="Y5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z5">
         <v>31</v>
@@ -3419,7 +3419,7 @@
         <v>61</v>
       </c>
       <c r="AB5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC5">
         <v>32</v>
@@ -3431,16 +3431,16 @@
         <v>900</v>
       </c>
       <c r="AF5" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG5" t="s">
         <v>137</v>
       </c>
-      <c r="AG5" t="s">
+      <c r="AH5" t="s">
         <v>138</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="AI5" t="s">
         <v>139</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>140</v>
       </c>
       <c r="AJ5">
         <v>10</v>
@@ -3449,7 +3449,7 @@
         <v>1.5</v>
       </c>
       <c r="AL5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AM5">
         <v>1.42</v>
@@ -3476,22 +3476,22 @@
         <v>120</v>
       </c>
       <c r="AU5" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV5" t="s">
         <v>142</v>
       </c>
-      <c r="AV5" t="s">
-        <v>143</v>
-      </c>
       <c r="AW5" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX5" t="s">
         <v>137</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="AY5" t="s">
         <v>138</v>
       </c>
-      <c r="AY5" t="s">
+      <c r="AZ5" t="s">
         <v>139</v>
-      </c>
-      <c r="AZ5" t="s">
-        <v>140</v>
       </c>
       <c r="BA5">
         <v>10</v>
@@ -3500,7 +3500,7 @@
         <v>1.5</v>
       </c>
       <c r="BC5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD5">
         <v>20</v>
@@ -3509,31 +3509,31 @@
         <v>1.5</v>
       </c>
       <c r="BF5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BG5">
         <v>1.42</v>
       </c>
       <c r="BH5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI5">
         <v>1.42</v>
       </c>
       <c r="BJ5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK5">
         <v>1.42</v>
       </c>
       <c r="BL5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BM5">
         <v>1.42</v>
       </c>
       <c r="BN5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BO5">
         <v>1.42</v>
@@ -3548,22 +3548,22 @@
         <v>120</v>
       </c>
       <c r="BS5" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT5" t="s">
         <v>142</v>
       </c>
-      <c r="BT5" t="s">
-        <v>143</v>
-      </c>
       <c r="BU5" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV5" t="s">
         <v>137</v>
       </c>
-      <c r="BV5" t="s">
+      <c r="BW5" t="s">
         <v>138</v>
       </c>
-      <c r="BW5" t="s">
+      <c r="BX5" t="s">
         <v>139</v>
-      </c>
-      <c r="BX5" t="s">
-        <v>140</v>
       </c>
       <c r="BY5">
         <v>10</v>
@@ -3572,13 +3572,13 @@
         <v>1.5</v>
       </c>
       <c r="CA5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CB5">
         <v>1.42</v>
       </c>
       <c r="CC5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CD5">
         <v>1.42</v>
@@ -3614,22 +3614,22 @@
         <v>120</v>
       </c>
       <c r="CO5" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP5" t="s">
         <v>142</v>
       </c>
-      <c r="CP5" t="s">
-        <v>143</v>
-      </c>
       <c r="CQ5" t="s">
+        <v>136</v>
+      </c>
+      <c r="CR5" t="s">
         <v>137</v>
       </c>
-      <c r="CR5" t="s">
+      <c r="CS5" t="s">
         <v>138</v>
       </c>
-      <c r="CS5" t="s">
+      <c r="CT5" t="s">
         <v>139</v>
-      </c>
-      <c r="CT5" t="s">
-        <v>140</v>
       </c>
       <c r="CU5">
         <v>10</v>
@@ -3638,19 +3638,19 @@
         <v>1.5</v>
       </c>
       <c r="CW5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CX5">
         <v>1.42</v>
       </c>
       <c r="CY5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CZ5">
         <v>1.42</v>
       </c>
       <c r="DA5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="DB5">
         <v>128</v>
@@ -3692,19 +3692,19 @@
         <v>120</v>
       </c>
       <c r="DO5" t="s">
+        <v>141</v>
+      </c>
+      <c r="DP5" t="s">
         <v>142</v>
       </c>
-      <c r="DP5" t="s">
-        <v>143</v>
-      </c>
       <c r="DQ5" t="s">
+        <v>144</v>
+      </c>
+      <c r="DR5" t="s">
         <v>145</v>
       </c>
-      <c r="DR5" t="s">
+      <c r="DS5" t="s">
         <v>146</v>
-      </c>
-      <c r="DS5" t="s">
-        <v>147</v>
       </c>
       <c r="DT5" t="b">
         <v>1</v>
@@ -3740,16 +3740,16 @@
         <v>1.5</v>
       </c>
       <c r="EE5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="EF5" t="s">
+        <v>144</v>
+      </c>
+      <c r="EG5" t="s">
         <v>145</v>
       </c>
-      <c r="EG5" t="s">
+      <c r="EH5" t="s">
         <v>146</v>
-      </c>
-      <c r="EH5" t="s">
-        <v>147</v>
       </c>
       <c r="EI5" t="b">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>1.5</v>
       </c>
       <c r="ET5" t="s">
+        <v>147</v>
+      </c>
+      <c r="EU5" t="s">
         <v>148</v>
       </c>
-      <c r="EU5" t="s">
+      <c r="EV5" t="s">
         <v>149</v>
       </c>
-      <c r="EV5" t="s">
+      <c r="EW5" t="s">
         <v>150</v>
-      </c>
-      <c r="EW5" t="s">
-        <v>151</v>
       </c>
       <c r="EX5">
         <v>9.9999999999999995E-7</v>
@@ -3809,13 +3809,13 @@
         <v>25</v>
       </c>
       <c r="FB5" t="s">
+        <v>148</v>
+      </c>
+      <c r="FC5" t="s">
         <v>149</v>
       </c>
-      <c r="FC5" t="s">
+      <c r="FD5" t="s">
         <v>150</v>
-      </c>
-      <c r="FD5" t="s">
-        <v>151</v>
       </c>
       <c r="FE5">
         <v>9.9999999999999995E-7</v>
@@ -3830,16 +3830,16 @@
         <v>25</v>
       </c>
       <c r="FI5" t="s">
+        <v>151</v>
+      </c>
+      <c r="FJ5" t="s">
+        <v>145</v>
+      </c>
+      <c r="FK5" t="s">
         <v>152</v>
       </c>
-      <c r="FJ5" t="s">
-        <v>146</v>
-      </c>
-      <c r="FK5" t="s">
+      <c r="FL5" t="s">
         <v>153</v>
-      </c>
-      <c r="FL5" t="s">
-        <v>154</v>
       </c>
       <c r="FM5">
         <v>200</v>
@@ -3866,7 +3866,7 @@
         <v>20</v>
       </c>
       <c r="FU5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="FV5">
         <v>532</v>
@@ -3887,19 +3887,19 @@
         <v>75</v>
       </c>
       <c r="GB5" t="s">
+        <v>155</v>
+      </c>
+      <c r="GC5" t="s">
         <v>156</v>
       </c>
-      <c r="GC5" t="s">
+      <c r="GD5" t="s">
+        <v>145</v>
+      </c>
+      <c r="GE5" t="s">
         <v>157</v>
       </c>
-      <c r="GD5" t="s">
-        <v>146</v>
-      </c>
-      <c r="GE5" t="s">
+      <c r="GF5" t="s">
         <v>158</v>
-      </c>
-      <c r="GF5" t="s">
-        <v>159</v>
       </c>
       <c r="GG5">
         <v>25</v>
@@ -3917,7 +3917,7 @@
         <v>250</v>
       </c>
       <c r="GL5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="GM5">
         <v>0.2</v>
@@ -3929,7 +3929,7 @@
         <v>25</v>
       </c>
       <c r="GP5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="GQ5">
         <v>0.1</v>
@@ -3944,19 +3944,19 @@
         <v>150</v>
       </c>
       <c r="GU5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="GV5">
         <v>35</v>
       </c>
       <c r="GW5" t="s">
+        <v>160</v>
+      </c>
+      <c r="GX5" t="s">
         <v>161</v>
       </c>
-      <c r="GX5" t="s">
+      <c r="GY5" t="s">
         <v>162</v>
-      </c>
-      <c r="GY5" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:207" x14ac:dyDescent="0.3">
@@ -3982,8 +3982,9 @@
       <c r="G6" t="s">
         <v>130</v>
       </c>
-      <c r="H6" t="s">
-        <v>131</v>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>6.25</v>
       </c>
       <c r="I6">
         <v>0.16</v>
@@ -3995,19 +3996,19 @@
         <v>0.16</v>
       </c>
       <c r="L6" t="s">
+        <v>131</v>
+      </c>
+      <c r="M6" t="s">
         <v>132</v>
-      </c>
-      <c r="M6" t="s">
-        <v>133</v>
       </c>
       <c r="N6">
         <v>1</v>
       </c>
       <c r="O6" t="s">
+        <v>133</v>
+      </c>
+      <c r="P6" t="s">
         <v>134</v>
-      </c>
-      <c r="P6" t="s">
-        <v>135</v>
       </c>
       <c r="Q6">
         <v>31</v>
@@ -4016,7 +4017,7 @@
         <v>61</v>
       </c>
       <c r="S6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T6">
         <v>32</v>
@@ -4025,7 +4026,7 @@
         <v>62</v>
       </c>
       <c r="V6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W6">
         <v>180</v>
@@ -4034,7 +4035,7 @@
         <v>50</v>
       </c>
       <c r="Y6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z6">
         <v>31</v>
@@ -4043,7 +4044,7 @@
         <v>61</v>
       </c>
       <c r="AB6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC6">
         <v>32</v>
@@ -4055,16 +4056,16 @@
         <v>900</v>
       </c>
       <c r="AF6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG6" t="s">
         <v>137</v>
       </c>
-      <c r="AG6" t="s">
+      <c r="AH6" t="s">
         <v>138</v>
       </c>
-      <c r="AH6" t="s">
+      <c r="AI6" t="s">
         <v>139</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>140</v>
       </c>
       <c r="AJ6">
         <v>10</v>
@@ -4073,7 +4074,7 @@
         <v>1.5</v>
       </c>
       <c r="AL6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AM6">
         <v>1.42</v>
@@ -4100,22 +4101,22 @@
         <v>120</v>
       </c>
       <c r="AU6" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV6" t="s">
         <v>142</v>
       </c>
-      <c r="AV6" t="s">
-        <v>143</v>
-      </c>
       <c r="AW6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX6" t="s">
         <v>137</v>
       </c>
-      <c r="AX6" t="s">
+      <c r="AY6" t="s">
         <v>138</v>
       </c>
-      <c r="AY6" t="s">
+      <c r="AZ6" t="s">
         <v>139</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>140</v>
       </c>
       <c r="BA6">
         <v>10</v>
@@ -4124,7 +4125,7 @@
         <v>1.5</v>
       </c>
       <c r="BC6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD6">
         <v>20</v>
@@ -4133,31 +4134,31 @@
         <v>1.5</v>
       </c>
       <c r="BF6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BG6">
         <v>1.42</v>
       </c>
       <c r="BH6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI6">
         <v>1.42</v>
       </c>
       <c r="BJ6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK6">
         <v>1.42</v>
       </c>
       <c r="BL6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BM6">
         <v>1.42</v>
       </c>
       <c r="BN6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BO6">
         <v>1.42</v>
@@ -4172,22 +4173,22 @@
         <v>120</v>
       </c>
       <c r="BS6" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT6" t="s">
         <v>142</v>
       </c>
-      <c r="BT6" t="s">
-        <v>143</v>
-      </c>
       <c r="BU6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV6" t="s">
         <v>137</v>
       </c>
-      <c r="BV6" t="s">
+      <c r="BW6" t="s">
         <v>138</v>
       </c>
-      <c r="BW6" t="s">
+      <c r="BX6" t="s">
         <v>139</v>
-      </c>
-      <c r="BX6" t="s">
-        <v>140</v>
       </c>
       <c r="BY6">
         <v>10</v>
@@ -4196,13 +4197,13 @@
         <v>1.5</v>
       </c>
       <c r="CA6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CB6">
         <v>1.42</v>
       </c>
       <c r="CC6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CD6">
         <v>1.42</v>
@@ -4238,22 +4239,22 @@
         <v>120</v>
       </c>
       <c r="CO6" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP6" t="s">
         <v>142</v>
       </c>
-      <c r="CP6" t="s">
-        <v>143</v>
-      </c>
       <c r="CQ6" t="s">
+        <v>136</v>
+      </c>
+      <c r="CR6" t="s">
         <v>137</v>
       </c>
-      <c r="CR6" t="s">
+      <c r="CS6" t="s">
         <v>138</v>
       </c>
-      <c r="CS6" t="s">
+      <c r="CT6" t="s">
         <v>139</v>
-      </c>
-      <c r="CT6" t="s">
-        <v>140</v>
       </c>
       <c r="CU6">
         <v>10</v>
@@ -4262,19 +4263,19 @@
         <v>1.5</v>
       </c>
       <c r="CW6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CX6">
         <v>1.42</v>
       </c>
       <c r="CY6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CZ6">
         <v>1.42</v>
       </c>
       <c r="DA6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="DB6">
         <v>128</v>
@@ -4316,19 +4317,19 @@
         <v>120</v>
       </c>
       <c r="DO6" t="s">
+        <v>141</v>
+      </c>
+      <c r="DP6" t="s">
         <v>142</v>
       </c>
-      <c r="DP6" t="s">
-        <v>143</v>
-      </c>
       <c r="DQ6" t="s">
+        <v>144</v>
+      </c>
+      <c r="DR6" t="s">
         <v>145</v>
       </c>
-      <c r="DR6" t="s">
+      <c r="DS6" t="s">
         <v>146</v>
-      </c>
-      <c r="DS6" t="s">
-        <v>147</v>
       </c>
       <c r="DT6" t="b">
         <v>1</v>
@@ -4364,16 +4365,16 @@
         <v>1.5</v>
       </c>
       <c r="EE6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="EF6" t="s">
+        <v>144</v>
+      </c>
+      <c r="EG6" t="s">
         <v>145</v>
       </c>
-      <c r="EG6" t="s">
+      <c r="EH6" t="s">
         <v>146</v>
-      </c>
-      <c r="EH6" t="s">
-        <v>147</v>
       </c>
       <c r="EI6" t="b">
         <v>0</v>
@@ -4409,16 +4410,16 @@
         <v>1.5</v>
       </c>
       <c r="ET6" t="s">
+        <v>147</v>
+      </c>
+      <c r="EU6" t="s">
         <v>148</v>
       </c>
-      <c r="EU6" t="s">
+      <c r="EV6" t="s">
         <v>149</v>
       </c>
-      <c r="EV6" t="s">
+      <c r="EW6" t="s">
         <v>150</v>
-      </c>
-      <c r="EW6" t="s">
-        <v>151</v>
       </c>
       <c r="EX6">
         <v>9.9999999999999995E-7</v>
@@ -4433,13 +4434,13 @@
         <v>25</v>
       </c>
       <c r="FB6" t="s">
+        <v>148</v>
+      </c>
+      <c r="FC6" t="s">
         <v>149</v>
       </c>
-      <c r="FC6" t="s">
+      <c r="FD6" t="s">
         <v>150</v>
-      </c>
-      <c r="FD6" t="s">
-        <v>151</v>
       </c>
       <c r="FE6">
         <v>9.9999999999999995E-7</v>
@@ -4454,16 +4455,16 @@
         <v>25</v>
       </c>
       <c r="FI6" t="s">
+        <v>151</v>
+      </c>
+      <c r="FJ6" t="s">
+        <v>145</v>
+      </c>
+      <c r="FK6" t="s">
         <v>152</v>
       </c>
-      <c r="FJ6" t="s">
-        <v>146</v>
-      </c>
-      <c r="FK6" t="s">
+      <c r="FL6" t="s">
         <v>153</v>
-      </c>
-      <c r="FL6" t="s">
-        <v>154</v>
       </c>
       <c r="FM6">
         <v>200</v>
@@ -4490,7 +4491,7 @@
         <v>20</v>
       </c>
       <c r="FU6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="FV6">
         <v>532</v>
@@ -4511,19 +4512,19 @@
         <v>75</v>
       </c>
       <c r="GB6" t="s">
+        <v>155</v>
+      </c>
+      <c r="GC6" t="s">
         <v>156</v>
       </c>
-      <c r="GC6" t="s">
+      <c r="GD6" t="s">
+        <v>145</v>
+      </c>
+      <c r="GE6" t="s">
         <v>157</v>
       </c>
-      <c r="GD6" t="s">
-        <v>146</v>
-      </c>
-      <c r="GE6" t="s">
+      <c r="GF6" t="s">
         <v>158</v>
-      </c>
-      <c r="GF6" t="s">
-        <v>159</v>
       </c>
       <c r="GG6">
         <v>25</v>
@@ -4541,7 +4542,7 @@
         <v>250</v>
       </c>
       <c r="GL6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="GM6">
         <v>0.2</v>
@@ -4553,7 +4554,7 @@
         <v>25</v>
       </c>
       <c r="GP6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="GQ6">
         <v>0.1</v>
@@ -4568,19 +4569,19 @@
         <v>150</v>
       </c>
       <c r="GU6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="GV6">
         <v>35</v>
       </c>
       <c r="GW6" t="s">
+        <v>160</v>
+      </c>
+      <c r="GX6" t="s">
         <v>161</v>
       </c>
-      <c r="GX6" t="s">
+      <c r="GY6" t="s">
         <v>162</v>
-      </c>
-      <c r="GY6" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:207" x14ac:dyDescent="0.3">
@@ -4606,8 +4607,9 @@
       <c r="G7" t="s">
         <v>130</v>
       </c>
-      <c r="H7" t="s">
-        <v>131</v>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>6.25</v>
       </c>
       <c r="I7">
         <v>0.16</v>
@@ -4619,19 +4621,19 @@
         <v>0.16</v>
       </c>
       <c r="L7" t="s">
+        <v>131</v>
+      </c>
+      <c r="M7" t="s">
         <v>132</v>
-      </c>
-      <c r="M7" t="s">
-        <v>133</v>
       </c>
       <c r="N7">
         <v>1</v>
       </c>
       <c r="O7" t="s">
+        <v>133</v>
+      </c>
+      <c r="P7" t="s">
         <v>134</v>
-      </c>
-      <c r="P7" t="s">
-        <v>135</v>
       </c>
       <c r="Q7">
         <v>31</v>
@@ -4640,7 +4642,7 @@
         <v>61</v>
       </c>
       <c r="S7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T7">
         <v>32</v>
@@ -4649,7 +4651,7 @@
         <v>62</v>
       </c>
       <c r="V7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W7">
         <v>180</v>
@@ -4658,7 +4660,7 @@
         <v>50</v>
       </c>
       <c r="Y7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z7">
         <v>31</v>
@@ -4667,7 +4669,7 @@
         <v>61</v>
       </c>
       <c r="AB7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC7">
         <v>32</v>
@@ -4679,16 +4681,16 @@
         <v>900</v>
       </c>
       <c r="AF7" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG7" t="s">
         <v>137</v>
       </c>
-      <c r="AG7" t="s">
+      <c r="AH7" t="s">
         <v>138</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="AI7" t="s">
         <v>139</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>140</v>
       </c>
       <c r="AJ7">
         <v>10</v>
@@ -4697,7 +4699,7 @@
         <v>1.5</v>
       </c>
       <c r="AL7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AM7">
         <v>1.42</v>
@@ -4724,22 +4726,22 @@
         <v>120</v>
       </c>
       <c r="AU7" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV7" t="s">
         <v>142</v>
       </c>
-      <c r="AV7" t="s">
-        <v>143</v>
-      </c>
       <c r="AW7" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX7" t="s">
         <v>137</v>
       </c>
-      <c r="AX7" t="s">
+      <c r="AY7" t="s">
         <v>138</v>
       </c>
-      <c r="AY7" t="s">
+      <c r="AZ7" t="s">
         <v>139</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>140</v>
       </c>
       <c r="BA7">
         <v>10</v>
@@ -4748,7 +4750,7 @@
         <v>1.5</v>
       </c>
       <c r="BC7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD7">
         <v>20</v>
@@ -4757,31 +4759,31 @@
         <v>1.5</v>
       </c>
       <c r="BF7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BG7">
         <v>1.42</v>
       </c>
       <c r="BH7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI7">
         <v>1.42</v>
       </c>
       <c r="BJ7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK7">
         <v>1.42</v>
       </c>
       <c r="BL7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BM7">
         <v>1.42</v>
       </c>
       <c r="BN7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BO7">
         <v>1.42</v>
@@ -4796,22 +4798,22 @@
         <v>120</v>
       </c>
       <c r="BS7" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT7" t="s">
         <v>142</v>
       </c>
-      <c r="BT7" t="s">
-        <v>143</v>
-      </c>
       <c r="BU7" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV7" t="s">
         <v>137</v>
       </c>
-      <c r="BV7" t="s">
+      <c r="BW7" t="s">
         <v>138</v>
       </c>
-      <c r="BW7" t="s">
+      <c r="BX7" t="s">
         <v>139</v>
-      </c>
-      <c r="BX7" t="s">
-        <v>140</v>
       </c>
       <c r="BY7">
         <v>10</v>
@@ -4820,13 +4822,13 @@
         <v>1.5</v>
       </c>
       <c r="CA7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CB7">
         <v>1.42</v>
       </c>
       <c r="CC7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CD7">
         <v>1.42</v>
@@ -4862,22 +4864,22 @@
         <v>120</v>
       </c>
       <c r="CO7" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP7" t="s">
         <v>142</v>
       </c>
-      <c r="CP7" t="s">
-        <v>143</v>
-      </c>
       <c r="CQ7" t="s">
+        <v>136</v>
+      </c>
+      <c r="CR7" t="s">
         <v>137</v>
       </c>
-      <c r="CR7" t="s">
+      <c r="CS7" t="s">
         <v>138</v>
       </c>
-      <c r="CS7" t="s">
+      <c r="CT7" t="s">
         <v>139</v>
-      </c>
-      <c r="CT7" t="s">
-        <v>140</v>
       </c>
       <c r="CU7">
         <v>10</v>
@@ -4886,19 +4888,19 @@
         <v>1.5</v>
       </c>
       <c r="CW7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CX7">
         <v>1.42</v>
       </c>
       <c r="CY7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CZ7">
         <v>1.42</v>
       </c>
       <c r="DA7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="DB7">
         <v>128</v>
@@ -4940,19 +4942,19 @@
         <v>120</v>
       </c>
       <c r="DO7" t="s">
+        <v>141</v>
+      </c>
+      <c r="DP7" t="s">
         <v>142</v>
       </c>
-      <c r="DP7" t="s">
-        <v>143</v>
-      </c>
       <c r="DQ7" t="s">
+        <v>144</v>
+      </c>
+      <c r="DR7" t="s">
         <v>145</v>
       </c>
-      <c r="DR7" t="s">
+      <c r="DS7" t="s">
         <v>146</v>
-      </c>
-      <c r="DS7" t="s">
-        <v>147</v>
       </c>
       <c r="DT7" t="b">
         <v>1</v>
@@ -4988,16 +4990,16 @@
         <v>1.5</v>
       </c>
       <c r="EE7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="EF7" t="s">
+        <v>144</v>
+      </c>
+      <c r="EG7" t="s">
         <v>145</v>
       </c>
-      <c r="EG7" t="s">
+      <c r="EH7" t="s">
         <v>146</v>
-      </c>
-      <c r="EH7" t="s">
-        <v>147</v>
       </c>
       <c r="EI7" t="b">
         <v>0</v>
@@ -5033,16 +5035,16 @@
         <v>1.5</v>
       </c>
       <c r="ET7" t="s">
+        <v>147</v>
+      </c>
+      <c r="EU7" t="s">
         <v>148</v>
       </c>
-      <c r="EU7" t="s">
+      <c r="EV7" t="s">
         <v>149</v>
       </c>
-      <c r="EV7" t="s">
+      <c r="EW7" t="s">
         <v>150</v>
-      </c>
-      <c r="EW7" t="s">
-        <v>151</v>
       </c>
       <c r="EX7">
         <v>9.9999999999999995E-7</v>
@@ -5057,13 +5059,13 @@
         <v>25</v>
       </c>
       <c r="FB7" t="s">
+        <v>148</v>
+      </c>
+      <c r="FC7" t="s">
         <v>149</v>
       </c>
-      <c r="FC7" t="s">
+      <c r="FD7" t="s">
         <v>150</v>
-      </c>
-      <c r="FD7" t="s">
-        <v>151</v>
       </c>
       <c r="FE7">
         <v>9.9999999999999995E-7</v>
@@ -5078,16 +5080,16 @@
         <v>25</v>
       </c>
       <c r="FI7" t="s">
+        <v>151</v>
+      </c>
+      <c r="FJ7" t="s">
+        <v>145</v>
+      </c>
+      <c r="FK7" t="s">
         <v>152</v>
       </c>
-      <c r="FJ7" t="s">
-        <v>146</v>
-      </c>
-      <c r="FK7" t="s">
+      <c r="FL7" t="s">
         <v>153</v>
-      </c>
-      <c r="FL7" t="s">
-        <v>154</v>
       </c>
       <c r="FM7">
         <v>200</v>
@@ -5114,7 +5116,7 @@
         <v>20</v>
       </c>
       <c r="FU7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="FV7">
         <v>532</v>
@@ -5135,19 +5137,19 @@
         <v>75</v>
       </c>
       <c r="GB7" t="s">
+        <v>155</v>
+      </c>
+      <c r="GC7" t="s">
         <v>156</v>
       </c>
-      <c r="GC7" t="s">
+      <c r="GD7" t="s">
+        <v>145</v>
+      </c>
+      <c r="GE7" t="s">
         <v>157</v>
       </c>
-      <c r="GD7" t="s">
-        <v>146</v>
-      </c>
-      <c r="GE7" t="s">
+      <c r="GF7" t="s">
         <v>158</v>
-      </c>
-      <c r="GF7" t="s">
-        <v>159</v>
       </c>
       <c r="GG7">
         <v>25</v>
@@ -5165,7 +5167,7 @@
         <v>250</v>
       </c>
       <c r="GL7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="GM7">
         <v>0.2</v>
@@ -5177,7 +5179,7 @@
         <v>25</v>
       </c>
       <c r="GP7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="GQ7">
         <v>0.1</v>
@@ -5192,19 +5194,19 @@
         <v>150</v>
       </c>
       <c r="GU7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="GV7">
         <v>35</v>
       </c>
       <c r="GW7" t="s">
+        <v>160</v>
+      </c>
+      <c r="GX7" t="s">
         <v>161</v>
       </c>
-      <c r="GX7" t="s">
+      <c r="GY7" t="s">
         <v>162</v>
-      </c>
-      <c r="GY7" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:207" x14ac:dyDescent="0.3">
@@ -5230,8 +5232,9 @@
       <c r="G8" t="s">
         <v>130</v>
       </c>
-      <c r="H8" t="s">
-        <v>131</v>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>6.25</v>
       </c>
       <c r="I8">
         <v>0.16</v>
@@ -5243,19 +5246,19 @@
         <v>0.16</v>
       </c>
       <c r="L8" t="s">
+        <v>131</v>
+      </c>
+      <c r="M8" t="s">
         <v>132</v>
-      </c>
-      <c r="M8" t="s">
-        <v>133</v>
       </c>
       <c r="N8">
         <v>1</v>
       </c>
       <c r="O8" t="s">
+        <v>133</v>
+      </c>
+      <c r="P8" t="s">
         <v>134</v>
-      </c>
-      <c r="P8" t="s">
-        <v>135</v>
       </c>
       <c r="Q8">
         <v>31</v>
@@ -5264,7 +5267,7 @@
         <v>61</v>
       </c>
       <c r="S8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T8">
         <v>32</v>
@@ -5273,7 +5276,7 @@
         <v>62</v>
       </c>
       <c r="V8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W8">
         <v>180</v>
@@ -5282,7 +5285,7 @@
         <v>50</v>
       </c>
       <c r="Y8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z8">
         <v>31</v>
@@ -5291,7 +5294,7 @@
         <v>61</v>
       </c>
       <c r="AB8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC8">
         <v>32</v>
@@ -5303,16 +5306,16 @@
         <v>900</v>
       </c>
       <c r="AF8" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG8" t="s">
         <v>137</v>
       </c>
-      <c r="AG8" t="s">
+      <c r="AH8" t="s">
         <v>138</v>
       </c>
-      <c r="AH8" t="s">
+      <c r="AI8" t="s">
         <v>139</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>140</v>
       </c>
       <c r="AJ8">
         <v>10</v>
@@ -5321,7 +5324,7 @@
         <v>1.5</v>
       </c>
       <c r="AL8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AM8">
         <v>1.42</v>
@@ -5348,22 +5351,22 @@
         <v>120</v>
       </c>
       <c r="AU8" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV8" t="s">
         <v>142</v>
       </c>
-      <c r="AV8" t="s">
-        <v>143</v>
-      </c>
       <c r="AW8" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX8" t="s">
         <v>137</v>
       </c>
-      <c r="AX8" t="s">
+      <c r="AY8" t="s">
         <v>138</v>
       </c>
-      <c r="AY8" t="s">
+      <c r="AZ8" t="s">
         <v>139</v>
-      </c>
-      <c r="AZ8" t="s">
-        <v>140</v>
       </c>
       <c r="BA8">
         <v>10</v>
@@ -5372,7 +5375,7 @@
         <v>1.5</v>
       </c>
       <c r="BC8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD8">
         <v>20</v>
@@ -5381,31 +5384,31 @@
         <v>1.5</v>
       </c>
       <c r="BF8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BG8">
         <v>1.42</v>
       </c>
       <c r="BH8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI8">
         <v>1.42</v>
       </c>
       <c r="BJ8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK8">
         <v>1.42</v>
       </c>
       <c r="BL8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BM8">
         <v>1.42</v>
       </c>
       <c r="BN8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BO8">
         <v>1.42</v>
@@ -5420,22 +5423,22 @@
         <v>120</v>
       </c>
       <c r="BS8" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT8" t="s">
         <v>142</v>
       </c>
-      <c r="BT8" t="s">
-        <v>143</v>
-      </c>
       <c r="BU8" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV8" t="s">
         <v>137</v>
       </c>
-      <c r="BV8" t="s">
+      <c r="BW8" t="s">
         <v>138</v>
       </c>
-      <c r="BW8" t="s">
+      <c r="BX8" t="s">
         <v>139</v>
-      </c>
-      <c r="BX8" t="s">
-        <v>140</v>
       </c>
       <c r="BY8">
         <v>10</v>
@@ -5444,13 +5447,13 @@
         <v>1.5</v>
       </c>
       <c r="CA8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CB8">
         <v>1.42</v>
       </c>
       <c r="CC8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CD8">
         <v>1.42</v>
@@ -5486,22 +5489,22 @@
         <v>120</v>
       </c>
       <c r="CO8" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP8" t="s">
         <v>142</v>
       </c>
-      <c r="CP8" t="s">
-        <v>143</v>
-      </c>
       <c r="CQ8" t="s">
+        <v>136</v>
+      </c>
+      <c r="CR8" t="s">
         <v>137</v>
       </c>
-      <c r="CR8" t="s">
+      <c r="CS8" t="s">
         <v>138</v>
       </c>
-      <c r="CS8" t="s">
+      <c r="CT8" t="s">
         <v>139</v>
-      </c>
-      <c r="CT8" t="s">
-        <v>140</v>
       </c>
       <c r="CU8">
         <v>10</v>
@@ -5510,19 +5513,19 @@
         <v>1.5</v>
       </c>
       <c r="CW8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CX8">
         <v>1.42</v>
       </c>
       <c r="CY8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CZ8">
         <v>1.42</v>
       </c>
       <c r="DA8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="DB8">
         <v>128</v>
@@ -5564,19 +5567,19 @@
         <v>120</v>
       </c>
       <c r="DO8" t="s">
+        <v>141</v>
+      </c>
+      <c r="DP8" t="s">
         <v>142</v>
       </c>
-      <c r="DP8" t="s">
-        <v>143</v>
-      </c>
       <c r="DQ8" t="s">
+        <v>144</v>
+      </c>
+      <c r="DR8" t="s">
         <v>145</v>
       </c>
-      <c r="DR8" t="s">
+      <c r="DS8" t="s">
         <v>146</v>
-      </c>
-      <c r="DS8" t="s">
-        <v>147</v>
       </c>
       <c r="DT8" t="b">
         <v>1</v>
@@ -5612,16 +5615,16 @@
         <v>1.5</v>
       </c>
       <c r="EE8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="EF8" t="s">
+        <v>144</v>
+      </c>
+      <c r="EG8" t="s">
         <v>145</v>
       </c>
-      <c r="EG8" t="s">
+      <c r="EH8" t="s">
         <v>146</v>
-      </c>
-      <c r="EH8" t="s">
-        <v>147</v>
       </c>
       <c r="EI8" t="b">
         <v>0</v>
@@ -5657,16 +5660,16 @@
         <v>1.5</v>
       </c>
       <c r="ET8" t="s">
+        <v>147</v>
+      </c>
+      <c r="EU8" t="s">
         <v>148</v>
       </c>
-      <c r="EU8" t="s">
+      <c r="EV8" t="s">
         <v>149</v>
       </c>
-      <c r="EV8" t="s">
+      <c r="EW8" t="s">
         <v>150</v>
-      </c>
-      <c r="EW8" t="s">
-        <v>151</v>
       </c>
       <c r="EX8">
         <v>9.9999999999999995E-7</v>
@@ -5681,13 +5684,13 @@
         <v>25</v>
       </c>
       <c r="FB8" t="s">
+        <v>148</v>
+      </c>
+      <c r="FC8" t="s">
         <v>149</v>
       </c>
-      <c r="FC8" t="s">
+      <c r="FD8" t="s">
         <v>150</v>
-      </c>
-      <c r="FD8" t="s">
-        <v>151</v>
       </c>
       <c r="FE8">
         <v>9.9999999999999995E-7</v>
@@ -5702,16 +5705,16 @@
         <v>25</v>
       </c>
       <c r="FI8" t="s">
+        <v>151</v>
+      </c>
+      <c r="FJ8" t="s">
+        <v>145</v>
+      </c>
+      <c r="FK8" t="s">
         <v>152</v>
       </c>
-      <c r="FJ8" t="s">
-        <v>146</v>
-      </c>
-      <c r="FK8" t="s">
+      <c r="FL8" t="s">
         <v>153</v>
-      </c>
-      <c r="FL8" t="s">
-        <v>154</v>
       </c>
       <c r="FM8">
         <v>200</v>
@@ -5738,7 +5741,7 @@
         <v>20</v>
       </c>
       <c r="FU8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="FV8">
         <v>532</v>
@@ -5759,19 +5762,19 @@
         <v>75</v>
       </c>
       <c r="GB8" t="s">
+        <v>155</v>
+      </c>
+      <c r="GC8" t="s">
         <v>156</v>
       </c>
-      <c r="GC8" t="s">
+      <c r="GD8" t="s">
+        <v>145</v>
+      </c>
+      <c r="GE8" t="s">
         <v>157</v>
       </c>
-      <c r="GD8" t="s">
-        <v>146</v>
-      </c>
-      <c r="GE8" t="s">
+      <c r="GF8" t="s">
         <v>158</v>
-      </c>
-      <c r="GF8" t="s">
-        <v>159</v>
       </c>
       <c r="GG8">
         <v>25</v>
@@ -5789,7 +5792,7 @@
         <v>250</v>
       </c>
       <c r="GL8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="GM8">
         <v>0.2</v>
@@ -5801,7 +5804,7 @@
         <v>25</v>
       </c>
       <c r="GP8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="GQ8">
         <v>0.1</v>
@@ -5816,19 +5819,19 @@
         <v>150</v>
       </c>
       <c r="GU8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="GV8">
         <v>35</v>
       </c>
       <c r="GW8" t="s">
+        <v>160</v>
+      </c>
+      <c r="GX8" t="s">
         <v>161</v>
       </c>
-      <c r="GX8" t="s">
+      <c r="GY8" t="s">
         <v>162</v>
-      </c>
-      <c r="GY8" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:207" x14ac:dyDescent="0.3">
@@ -5854,8 +5857,9 @@
       <c r="G9" t="s">
         <v>130</v>
       </c>
-      <c r="H9" t="s">
-        <v>131</v>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>6.25</v>
       </c>
       <c r="I9">
         <v>0.16</v>
@@ -5867,19 +5871,19 @@
         <v>0.16</v>
       </c>
       <c r="L9" t="s">
+        <v>131</v>
+      </c>
+      <c r="M9" t="s">
         <v>132</v>
-      </c>
-      <c r="M9" t="s">
-        <v>133</v>
       </c>
       <c r="N9">
         <v>1</v>
       </c>
       <c r="O9" t="s">
+        <v>133</v>
+      </c>
+      <c r="P9" t="s">
         <v>134</v>
-      </c>
-      <c r="P9" t="s">
-        <v>135</v>
       </c>
       <c r="Q9">
         <v>31</v>
@@ -5888,7 +5892,7 @@
         <v>61</v>
       </c>
       <c r="S9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T9">
         <v>32</v>
@@ -5897,7 +5901,7 @@
         <v>62</v>
       </c>
       <c r="V9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W9">
         <v>180</v>
@@ -5906,7 +5910,7 @@
         <v>50</v>
       </c>
       <c r="Y9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z9">
         <v>31</v>
@@ -5915,7 +5919,7 @@
         <v>61</v>
       </c>
       <c r="AB9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC9">
         <v>32</v>
@@ -5927,16 +5931,16 @@
         <v>900</v>
       </c>
       <c r="AF9" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG9" t="s">
         <v>137</v>
       </c>
-      <c r="AG9" t="s">
+      <c r="AH9" t="s">
         <v>138</v>
       </c>
-      <c r="AH9" t="s">
+      <c r="AI9" t="s">
         <v>139</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>140</v>
       </c>
       <c r="AJ9">
         <v>10</v>
@@ -5945,7 +5949,7 @@
         <v>1.5</v>
       </c>
       <c r="AL9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AM9">
         <v>1.42</v>
@@ -5972,22 +5976,22 @@
         <v>120</v>
       </c>
       <c r="AU9" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV9" t="s">
         <v>142</v>
       </c>
-      <c r="AV9" t="s">
-        <v>143</v>
-      </c>
       <c r="AW9" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX9" t="s">
         <v>137</v>
       </c>
-      <c r="AX9" t="s">
+      <c r="AY9" t="s">
         <v>138</v>
       </c>
-      <c r="AY9" t="s">
+      <c r="AZ9" t="s">
         <v>139</v>
-      </c>
-      <c r="AZ9" t="s">
-        <v>140</v>
       </c>
       <c r="BA9">
         <v>10</v>
@@ -5996,7 +6000,7 @@
         <v>1.5</v>
       </c>
       <c r="BC9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD9">
         <v>20</v>
@@ -6005,31 +6009,31 @@
         <v>1.5</v>
       </c>
       <c r="BF9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BG9">
         <v>1.42</v>
       </c>
       <c r="BH9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI9">
         <v>1.42</v>
       </c>
       <c r="BJ9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK9">
         <v>1.42</v>
       </c>
       <c r="BL9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BM9">
         <v>1.42</v>
       </c>
       <c r="BN9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BO9">
         <v>1.42</v>
@@ -6044,22 +6048,22 @@
         <v>120</v>
       </c>
       <c r="BS9" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT9" t="s">
         <v>142</v>
       </c>
-      <c r="BT9" t="s">
-        <v>143</v>
-      </c>
       <c r="BU9" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV9" t="s">
         <v>137</v>
       </c>
-      <c r="BV9" t="s">
+      <c r="BW9" t="s">
         <v>138</v>
       </c>
-      <c r="BW9" t="s">
+      <c r="BX9" t="s">
         <v>139</v>
-      </c>
-      <c r="BX9" t="s">
-        <v>140</v>
       </c>
       <c r="BY9">
         <v>10</v>
@@ -6068,13 +6072,13 @@
         <v>1.5</v>
       </c>
       <c r="CA9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CB9">
         <v>1.42</v>
       </c>
       <c r="CC9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CD9">
         <v>1.42</v>
@@ -6110,22 +6114,22 @@
         <v>120</v>
       </c>
       <c r="CO9" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP9" t="s">
         <v>142</v>
       </c>
-      <c r="CP9" t="s">
-        <v>143</v>
-      </c>
       <c r="CQ9" t="s">
+        <v>136</v>
+      </c>
+      <c r="CR9" t="s">
         <v>137</v>
       </c>
-      <c r="CR9" t="s">
+      <c r="CS9" t="s">
         <v>138</v>
       </c>
-      <c r="CS9" t="s">
+      <c r="CT9" t="s">
         <v>139</v>
-      </c>
-      <c r="CT9" t="s">
-        <v>140</v>
       </c>
       <c r="CU9">
         <v>10</v>
@@ -6134,19 +6138,19 @@
         <v>1.5</v>
       </c>
       <c r="CW9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CX9">
         <v>1.42</v>
       </c>
       <c r="CY9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CZ9">
         <v>1.42</v>
       </c>
       <c r="DA9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="DB9">
         <v>128</v>
@@ -6188,19 +6192,19 @@
         <v>120</v>
       </c>
       <c r="DO9" t="s">
+        <v>141</v>
+      </c>
+      <c r="DP9" t="s">
         <v>142</v>
       </c>
-      <c r="DP9" t="s">
-        <v>143</v>
-      </c>
       <c r="DQ9" t="s">
+        <v>144</v>
+      </c>
+      <c r="DR9" t="s">
         <v>145</v>
       </c>
-      <c r="DR9" t="s">
+      <c r="DS9" t="s">
         <v>146</v>
-      </c>
-      <c r="DS9" t="s">
-        <v>147</v>
       </c>
       <c r="DT9" t="b">
         <v>1</v>
@@ -6236,16 +6240,16 @@
         <v>1.5</v>
       </c>
       <c r="EE9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="EF9" t="s">
+        <v>144</v>
+      </c>
+      <c r="EG9" t="s">
         <v>145</v>
       </c>
-      <c r="EG9" t="s">
+      <c r="EH9" t="s">
         <v>146</v>
-      </c>
-      <c r="EH9" t="s">
-        <v>147</v>
       </c>
       <c r="EI9" t="b">
         <v>0</v>
@@ -6281,16 +6285,16 @@
         <v>1.5</v>
       </c>
       <c r="ET9" t="s">
+        <v>147</v>
+      </c>
+      <c r="EU9" t="s">
         <v>148</v>
       </c>
-      <c r="EU9" t="s">
+      <c r="EV9" t="s">
         <v>149</v>
       </c>
-      <c r="EV9" t="s">
+      <c r="EW9" t="s">
         <v>150</v>
-      </c>
-      <c r="EW9" t="s">
-        <v>151</v>
       </c>
       <c r="EX9">
         <v>9.9999999999999995E-7</v>
@@ -6305,13 +6309,13 @@
         <v>25</v>
       </c>
       <c r="FB9" t="s">
+        <v>148</v>
+      </c>
+      <c r="FC9" t="s">
         <v>149</v>
       </c>
-      <c r="FC9" t="s">
+      <c r="FD9" t="s">
         <v>150</v>
-      </c>
-      <c r="FD9" t="s">
-        <v>151</v>
       </c>
       <c r="FE9">
         <v>9.9999999999999995E-7</v>
@@ -6326,16 +6330,16 @@
         <v>25</v>
       </c>
       <c r="FI9" t="s">
+        <v>151</v>
+      </c>
+      <c r="FJ9" t="s">
+        <v>145</v>
+      </c>
+      <c r="FK9" t="s">
         <v>152</v>
       </c>
-      <c r="FJ9" t="s">
-        <v>146</v>
-      </c>
-      <c r="FK9" t="s">
+      <c r="FL9" t="s">
         <v>153</v>
-      </c>
-      <c r="FL9" t="s">
-        <v>154</v>
       </c>
       <c r="FM9">
         <v>200</v>
@@ -6362,7 +6366,7 @@
         <v>20</v>
       </c>
       <c r="FU9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="FV9">
         <v>532</v>
@@ -6383,19 +6387,19 @@
         <v>75</v>
       </c>
       <c r="GB9" t="s">
+        <v>155</v>
+      </c>
+      <c r="GC9" t="s">
         <v>156</v>
       </c>
-      <c r="GC9" t="s">
+      <c r="GD9" t="s">
+        <v>145</v>
+      </c>
+      <c r="GE9" t="s">
         <v>157</v>
       </c>
-      <c r="GD9" t="s">
-        <v>146</v>
-      </c>
-      <c r="GE9" t="s">
+      <c r="GF9" t="s">
         <v>158</v>
-      </c>
-      <c r="GF9" t="s">
-        <v>159</v>
       </c>
       <c r="GG9">
         <v>25</v>
@@ -6413,7 +6417,7 @@
         <v>250</v>
       </c>
       <c r="GL9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="GM9">
         <v>0.2</v>
@@ -6425,7 +6429,7 @@
         <v>25</v>
       </c>
       <c r="GP9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="GQ9">
         <v>0.1</v>
@@ -6440,19 +6444,19 @@
         <v>150</v>
       </c>
       <c r="GU9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="GV9">
         <v>35</v>
       </c>
       <c r="GW9" t="s">
+        <v>160</v>
+      </c>
+      <c r="GX9" t="s">
         <v>161</v>
       </c>
-      <c r="GX9" t="s">
+      <c r="GY9" t="s">
         <v>162</v>
-      </c>
-      <c r="GY9" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:207" x14ac:dyDescent="0.3">
@@ -6478,8 +6482,9 @@
       <c r="G10" t="s">
         <v>130</v>
       </c>
-      <c r="H10" t="s">
-        <v>131</v>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>6.25</v>
       </c>
       <c r="I10">
         <v>0.16</v>
@@ -6491,19 +6496,19 @@
         <v>0.16</v>
       </c>
       <c r="L10" t="s">
+        <v>131</v>
+      </c>
+      <c r="M10" t="s">
         <v>132</v>
-      </c>
-      <c r="M10" t="s">
-        <v>133</v>
       </c>
       <c r="N10">
         <v>1</v>
       </c>
       <c r="O10" t="s">
+        <v>133</v>
+      </c>
+      <c r="P10" t="s">
         <v>134</v>
-      </c>
-      <c r="P10" t="s">
-        <v>135</v>
       </c>
       <c r="Q10">
         <v>31</v>
@@ -6512,7 +6517,7 @@
         <v>61</v>
       </c>
       <c r="S10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T10">
         <v>32</v>
@@ -6521,7 +6526,7 @@
         <v>62</v>
       </c>
       <c r="V10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W10">
         <v>180</v>
@@ -6530,7 +6535,7 @@
         <v>50</v>
       </c>
       <c r="Y10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z10">
         <v>31</v>
@@ -6539,7 +6544,7 @@
         <v>61</v>
       </c>
       <c r="AB10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC10">
         <v>32</v>
@@ -6551,16 +6556,16 @@
         <v>900</v>
       </c>
       <c r="AF10" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG10" t="s">
         <v>137</v>
       </c>
-      <c r="AG10" t="s">
+      <c r="AH10" t="s">
         <v>138</v>
       </c>
-      <c r="AH10" t="s">
+      <c r="AI10" t="s">
         <v>139</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>140</v>
       </c>
       <c r="AJ10">
         <v>10</v>
@@ -6569,7 +6574,7 @@
         <v>1.5</v>
       </c>
       <c r="AL10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AM10">
         <v>1.42</v>
@@ -6596,22 +6601,22 @@
         <v>120</v>
       </c>
       <c r="AU10" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV10" t="s">
         <v>142</v>
       </c>
-      <c r="AV10" t="s">
-        <v>143</v>
-      </c>
       <c r="AW10" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX10" t="s">
         <v>137</v>
       </c>
-      <c r="AX10" t="s">
+      <c r="AY10" t="s">
         <v>138</v>
       </c>
-      <c r="AY10" t="s">
+      <c r="AZ10" t="s">
         <v>139</v>
-      </c>
-      <c r="AZ10" t="s">
-        <v>140</v>
       </c>
       <c r="BA10">
         <v>10</v>
@@ -6620,7 +6625,7 @@
         <v>1.5</v>
       </c>
       <c r="BC10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD10">
         <v>20</v>
@@ -6629,31 +6634,31 @@
         <v>1.5</v>
       </c>
       <c r="BF10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BG10">
         <v>1.42</v>
       </c>
       <c r="BH10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI10">
         <v>1.42</v>
       </c>
       <c r="BJ10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK10">
         <v>1.42</v>
       </c>
       <c r="BL10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BM10">
         <v>1.42</v>
       </c>
       <c r="BN10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BO10">
         <v>1.42</v>
@@ -6668,22 +6673,22 @@
         <v>120</v>
       </c>
       <c r="BS10" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT10" t="s">
         <v>142</v>
       </c>
-      <c r="BT10" t="s">
-        <v>143</v>
-      </c>
       <c r="BU10" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV10" t="s">
         <v>137</v>
       </c>
-      <c r="BV10" t="s">
+      <c r="BW10" t="s">
         <v>138</v>
       </c>
-      <c r="BW10" t="s">
+      <c r="BX10" t="s">
         <v>139</v>
-      </c>
-      <c r="BX10" t="s">
-        <v>140</v>
       </c>
       <c r="BY10">
         <v>10</v>
@@ -6692,13 +6697,13 @@
         <v>1.5</v>
       </c>
       <c r="CA10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CB10">
         <v>1.42</v>
       </c>
       <c r="CC10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CD10">
         <v>1.42</v>
@@ -6734,22 +6739,22 @@
         <v>120</v>
       </c>
       <c r="CO10" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP10" t="s">
         <v>142</v>
       </c>
-      <c r="CP10" t="s">
-        <v>143</v>
-      </c>
       <c r="CQ10" t="s">
+        <v>136</v>
+      </c>
+      <c r="CR10" t="s">
         <v>137</v>
       </c>
-      <c r="CR10" t="s">
+      <c r="CS10" t="s">
         <v>138</v>
       </c>
-      <c r="CS10" t="s">
+      <c r="CT10" t="s">
         <v>139</v>
-      </c>
-      <c r="CT10" t="s">
-        <v>140</v>
       </c>
       <c r="CU10">
         <v>10</v>
@@ -6758,19 +6763,19 @@
         <v>1.5</v>
       </c>
       <c r="CW10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CX10">
         <v>1.42</v>
       </c>
       <c r="CY10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CZ10">
         <v>1.42</v>
       </c>
       <c r="DA10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="DB10">
         <v>128</v>
@@ -6812,19 +6817,19 @@
         <v>120</v>
       </c>
       <c r="DO10" t="s">
+        <v>141</v>
+      </c>
+      <c r="DP10" t="s">
         <v>142</v>
       </c>
-      <c r="DP10" t="s">
-        <v>143</v>
-      </c>
       <c r="DQ10" t="s">
+        <v>144</v>
+      </c>
+      <c r="DR10" t="s">
         <v>145</v>
       </c>
-      <c r="DR10" t="s">
+      <c r="DS10" t="s">
         <v>146</v>
-      </c>
-      <c r="DS10" t="s">
-        <v>147</v>
       </c>
       <c r="DT10" t="b">
         <v>1</v>
@@ -6860,16 +6865,16 @@
         <v>1.5</v>
       </c>
       <c r="EE10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="EF10" t="s">
+        <v>144</v>
+      </c>
+      <c r="EG10" t="s">
         <v>145</v>
       </c>
-      <c r="EG10" t="s">
+      <c r="EH10" t="s">
         <v>146</v>
-      </c>
-      <c r="EH10" t="s">
-        <v>147</v>
       </c>
       <c r="EI10" t="b">
         <v>0</v>
@@ -6905,16 +6910,16 @@
         <v>1.5</v>
       </c>
       <c r="ET10" t="s">
+        <v>147</v>
+      </c>
+      <c r="EU10" t="s">
         <v>148</v>
       </c>
-      <c r="EU10" t="s">
+      <c r="EV10" t="s">
         <v>149</v>
       </c>
-      <c r="EV10" t="s">
+      <c r="EW10" t="s">
         <v>150</v>
-      </c>
-      <c r="EW10" t="s">
-        <v>151</v>
       </c>
       <c r="EX10">
         <v>9.9999999999999995E-7</v>
@@ -6929,13 +6934,13 @@
         <v>25</v>
       </c>
       <c r="FB10" t="s">
+        <v>148</v>
+      </c>
+      <c r="FC10" t="s">
         <v>149</v>
       </c>
-      <c r="FC10" t="s">
+      <c r="FD10" t="s">
         <v>150</v>
-      </c>
-      <c r="FD10" t="s">
-        <v>151</v>
       </c>
       <c r="FE10">
         <v>9.9999999999999995E-7</v>
@@ -6950,16 +6955,16 @@
         <v>25</v>
       </c>
       <c r="FI10" t="s">
+        <v>151</v>
+      </c>
+      <c r="FJ10" t="s">
+        <v>145</v>
+      </c>
+      <c r="FK10" t="s">
         <v>152</v>
       </c>
-      <c r="FJ10" t="s">
-        <v>146</v>
-      </c>
-      <c r="FK10" t="s">
+      <c r="FL10" t="s">
         <v>153</v>
-      </c>
-      <c r="FL10" t="s">
-        <v>154</v>
       </c>
       <c r="FM10">
         <v>200</v>
@@ -6986,7 +6991,7 @@
         <v>20</v>
       </c>
       <c r="FU10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="FV10">
         <v>532</v>
@@ -7007,19 +7012,19 @@
         <v>75</v>
       </c>
       <c r="GB10" t="s">
+        <v>155</v>
+      </c>
+      <c r="GC10" t="s">
         <v>156</v>
       </c>
-      <c r="GC10" t="s">
+      <c r="GD10" t="s">
+        <v>145</v>
+      </c>
+      <c r="GE10" t="s">
         <v>157</v>
       </c>
-      <c r="GD10" t="s">
-        <v>146</v>
-      </c>
-      <c r="GE10" t="s">
+      <c r="GF10" t="s">
         <v>158</v>
-      </c>
-      <c r="GF10" t="s">
-        <v>159</v>
       </c>
       <c r="GG10">
         <v>25</v>
@@ -7037,7 +7042,7 @@
         <v>250</v>
       </c>
       <c r="GL10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="GM10">
         <v>0.2</v>
@@ -7049,7 +7054,7 @@
         <v>25</v>
       </c>
       <c r="GP10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="GQ10">
         <v>0.1</v>
@@ -7064,19 +7069,19 @@
         <v>150</v>
       </c>
       <c r="GU10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="GV10">
         <v>35</v>
       </c>
       <c r="GW10" t="s">
+        <v>160</v>
+      </c>
+      <c r="GX10" t="s">
         <v>161</v>
       </c>
-      <c r="GX10" t="s">
+      <c r="GY10" t="s">
         <v>162</v>
-      </c>
-      <c r="GY10" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:207" x14ac:dyDescent="0.3">
@@ -7102,8 +7107,9 @@
       <c r="G11" t="s">
         <v>130</v>
       </c>
-      <c r="H11" t="s">
-        <v>131</v>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>6.25</v>
       </c>
       <c r="I11">
         <v>0.16</v>
@@ -7115,19 +7121,19 @@
         <v>0.16</v>
       </c>
       <c r="L11" t="s">
+        <v>131</v>
+      </c>
+      <c r="M11" t="s">
         <v>132</v>
-      </c>
-      <c r="M11" t="s">
-        <v>133</v>
       </c>
       <c r="N11">
         <v>1</v>
       </c>
       <c r="O11" t="s">
+        <v>133</v>
+      </c>
+      <c r="P11" t="s">
         <v>134</v>
-      </c>
-      <c r="P11" t="s">
-        <v>135</v>
       </c>
       <c r="Q11">
         <v>31</v>
@@ -7136,7 +7142,7 @@
         <v>61</v>
       </c>
       <c r="S11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T11">
         <v>32</v>
@@ -7145,7 +7151,7 @@
         <v>62</v>
       </c>
       <c r="V11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W11">
         <v>180</v>
@@ -7154,7 +7160,7 @@
         <v>50</v>
       </c>
       <c r="Y11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z11">
         <v>31</v>
@@ -7163,7 +7169,7 @@
         <v>61</v>
       </c>
       <c r="AB11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC11">
         <v>32</v>
@@ -7175,16 +7181,16 @@
         <v>900</v>
       </c>
       <c r="AF11" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG11" t="s">
         <v>137</v>
       </c>
-      <c r="AG11" t="s">
+      <c r="AH11" t="s">
         <v>138</v>
       </c>
-      <c r="AH11" t="s">
+      <c r="AI11" t="s">
         <v>139</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>140</v>
       </c>
       <c r="AJ11">
         <v>10</v>
@@ -7193,7 +7199,7 @@
         <v>1.5</v>
       </c>
       <c r="AL11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AM11">
         <v>1.42</v>
@@ -7220,22 +7226,22 @@
         <v>120</v>
       </c>
       <c r="AU11" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV11" t="s">
         <v>142</v>
       </c>
-      <c r="AV11" t="s">
-        <v>143</v>
-      </c>
       <c r="AW11" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX11" t="s">
         <v>137</v>
       </c>
-      <c r="AX11" t="s">
+      <c r="AY11" t="s">
         <v>138</v>
       </c>
-      <c r="AY11" t="s">
+      <c r="AZ11" t="s">
         <v>139</v>
-      </c>
-      <c r="AZ11" t="s">
-        <v>140</v>
       </c>
       <c r="BA11">
         <v>10</v>
@@ -7244,7 +7250,7 @@
         <v>1.5</v>
       </c>
       <c r="BC11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD11">
         <v>20</v>
@@ -7253,31 +7259,31 @@
         <v>1.5</v>
       </c>
       <c r="BF11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BG11">
         <v>1.42</v>
       </c>
       <c r="BH11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI11">
         <v>1.42</v>
       </c>
       <c r="BJ11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK11">
         <v>1.42</v>
       </c>
       <c r="BL11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BM11">
         <v>1.42</v>
       </c>
       <c r="BN11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BO11">
         <v>1.42</v>
@@ -7292,22 +7298,22 @@
         <v>120</v>
       </c>
       <c r="BS11" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT11" t="s">
         <v>142</v>
       </c>
-      <c r="BT11" t="s">
-        <v>143</v>
-      </c>
       <c r="BU11" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV11" t="s">
         <v>137</v>
       </c>
-      <c r="BV11" t="s">
+      <c r="BW11" t="s">
         <v>138</v>
       </c>
-      <c r="BW11" t="s">
+      <c r="BX11" t="s">
         <v>139</v>
-      </c>
-      <c r="BX11" t="s">
-        <v>140</v>
       </c>
       <c r="BY11">
         <v>10</v>
@@ -7316,13 +7322,13 @@
         <v>1.5</v>
       </c>
       <c r="CA11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CB11">
         <v>1.42</v>
       </c>
       <c r="CC11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CD11">
         <v>1.42</v>
@@ -7358,22 +7364,22 @@
         <v>120</v>
       </c>
       <c r="CO11" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP11" t="s">
         <v>142</v>
       </c>
-      <c r="CP11" t="s">
-        <v>143</v>
-      </c>
       <c r="CQ11" t="s">
+        <v>136</v>
+      </c>
+      <c r="CR11" t="s">
         <v>137</v>
       </c>
-      <c r="CR11" t="s">
+      <c r="CS11" t="s">
         <v>138</v>
       </c>
-      <c r="CS11" t="s">
+      <c r="CT11" t="s">
         <v>139</v>
-      </c>
-      <c r="CT11" t="s">
-        <v>140</v>
       </c>
       <c r="CU11">
         <v>10</v>
@@ -7382,19 +7388,19 @@
         <v>1.5</v>
       </c>
       <c r="CW11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CX11">
         <v>1.42</v>
       </c>
       <c r="CY11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CZ11">
         <v>1.42</v>
       </c>
       <c r="DA11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="DB11">
         <v>128</v>
@@ -7436,19 +7442,19 @@
         <v>120</v>
       </c>
       <c r="DO11" t="s">
+        <v>141</v>
+      </c>
+      <c r="DP11" t="s">
         <v>142</v>
       </c>
-      <c r="DP11" t="s">
-        <v>143</v>
-      </c>
       <c r="DQ11" t="s">
+        <v>144</v>
+      </c>
+      <c r="DR11" t="s">
         <v>145</v>
       </c>
-      <c r="DR11" t="s">
+      <c r="DS11" t="s">
         <v>146</v>
-      </c>
-      <c r="DS11" t="s">
-        <v>147</v>
       </c>
       <c r="DT11" t="b">
         <v>1</v>
@@ -7484,16 +7490,16 @@
         <v>1.5</v>
       </c>
       <c r="EE11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="EF11" t="s">
+        <v>144</v>
+      </c>
+      <c r="EG11" t="s">
         <v>145</v>
       </c>
-      <c r="EG11" t="s">
+      <c r="EH11" t="s">
         <v>146</v>
-      </c>
-      <c r="EH11" t="s">
-        <v>147</v>
       </c>
       <c r="EI11" t="b">
         <v>0</v>
@@ -7529,16 +7535,16 @@
         <v>1.5</v>
       </c>
       <c r="ET11" t="s">
+        <v>147</v>
+      </c>
+      <c r="EU11" t="s">
         <v>148</v>
       </c>
-      <c r="EU11" t="s">
+      <c r="EV11" t="s">
         <v>149</v>
       </c>
-      <c r="EV11" t="s">
+      <c r="EW11" t="s">
         <v>150</v>
-      </c>
-      <c r="EW11" t="s">
-        <v>151</v>
       </c>
       <c r="EX11">
         <v>9.9999999999999995E-7</v>
@@ -7553,13 +7559,13 @@
         <v>25</v>
       </c>
       <c r="FB11" t="s">
+        <v>148</v>
+      </c>
+      <c r="FC11" t="s">
         <v>149</v>
       </c>
-      <c r="FC11" t="s">
+      <c r="FD11" t="s">
         <v>150</v>
-      </c>
-      <c r="FD11" t="s">
-        <v>151</v>
       </c>
       <c r="FE11">
         <v>9.9999999999999995E-7</v>
@@ -7574,16 +7580,16 @@
         <v>25</v>
       </c>
       <c r="FI11" t="s">
+        <v>151</v>
+      </c>
+      <c r="FJ11" t="s">
+        <v>145</v>
+      </c>
+      <c r="FK11" t="s">
         <v>152</v>
       </c>
-      <c r="FJ11" t="s">
-        <v>146</v>
-      </c>
-      <c r="FK11" t="s">
+      <c r="FL11" t="s">
         <v>153</v>
-      </c>
-      <c r="FL11" t="s">
-        <v>154</v>
       </c>
       <c r="FM11">
         <v>200</v>
@@ -7610,7 +7616,7 @@
         <v>20</v>
       </c>
       <c r="FU11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="FV11">
         <v>532</v>
@@ -7631,19 +7637,19 @@
         <v>75</v>
       </c>
       <c r="GB11" t="s">
+        <v>155</v>
+      </c>
+      <c r="GC11" t="s">
         <v>156</v>
       </c>
-      <c r="GC11" t="s">
+      <c r="GD11" t="s">
+        <v>145</v>
+      </c>
+      <c r="GE11" t="s">
         <v>157</v>
       </c>
-      <c r="GD11" t="s">
-        <v>146</v>
-      </c>
-      <c r="GE11" t="s">
+      <c r="GF11" t="s">
         <v>158</v>
-      </c>
-      <c r="GF11" t="s">
-        <v>159</v>
       </c>
       <c r="GG11">
         <v>25</v>
@@ -7661,7 +7667,7 @@
         <v>250</v>
       </c>
       <c r="GL11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="GM11">
         <v>0.2</v>
@@ -7673,7 +7679,7 @@
         <v>25</v>
       </c>
       <c r="GP11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="GQ11">
         <v>0.1</v>
@@ -7688,19 +7694,19 @@
         <v>150</v>
       </c>
       <c r="GU11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="GV11">
         <v>35</v>
       </c>
       <c r="GW11" t="s">
+        <v>160</v>
+      </c>
+      <c r="GX11" t="s">
         <v>161</v>
       </c>
-      <c r="GX11" t="s">
+      <c r="GY11" t="s">
         <v>162</v>
-      </c>
-      <c r="GY11" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:207" x14ac:dyDescent="0.3">
@@ -7726,8 +7732,9 @@
       <c r="G12" t="s">
         <v>130</v>
       </c>
-      <c r="H12" t="s">
-        <v>131</v>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>6.25</v>
       </c>
       <c r="I12">
         <v>0.16</v>
@@ -7739,19 +7746,19 @@
         <v>0.16</v>
       </c>
       <c r="L12" t="s">
+        <v>131</v>
+      </c>
+      <c r="M12" t="s">
         <v>132</v>
-      </c>
-      <c r="M12" t="s">
-        <v>133</v>
       </c>
       <c r="N12">
         <v>1</v>
       </c>
       <c r="O12" t="s">
+        <v>133</v>
+      </c>
+      <c r="P12" t="s">
         <v>134</v>
-      </c>
-      <c r="P12" t="s">
-        <v>135</v>
       </c>
       <c r="Q12">
         <v>31</v>
@@ -7760,7 +7767,7 @@
         <v>61</v>
       </c>
       <c r="S12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T12">
         <v>32</v>
@@ -7769,7 +7776,7 @@
         <v>62</v>
       </c>
       <c r="V12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W12">
         <v>180</v>
@@ -7778,7 +7785,7 @@
         <v>50</v>
       </c>
       <c r="Y12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z12">
         <v>31</v>
@@ -7787,7 +7794,7 @@
         <v>61</v>
       </c>
       <c r="AB12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC12">
         <v>32</v>
@@ -7799,16 +7806,16 @@
         <v>900</v>
       </c>
       <c r="AF12" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG12" t="s">
         <v>137</v>
       </c>
-      <c r="AG12" t="s">
+      <c r="AH12" t="s">
         <v>138</v>
       </c>
-      <c r="AH12" t="s">
+      <c r="AI12" t="s">
         <v>139</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>140</v>
       </c>
       <c r="AJ12">
         <v>10</v>
@@ -7817,7 +7824,7 @@
         <v>1.5</v>
       </c>
       <c r="AL12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AM12">
         <v>1.42</v>
@@ -7844,22 +7851,22 @@
         <v>120</v>
       </c>
       <c r="AU12" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV12" t="s">
         <v>142</v>
       </c>
-      <c r="AV12" t="s">
-        <v>143</v>
-      </c>
       <c r="AW12" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX12" t="s">
         <v>137</v>
       </c>
-      <c r="AX12" t="s">
+      <c r="AY12" t="s">
         <v>138</v>
       </c>
-      <c r="AY12" t="s">
+      <c r="AZ12" t="s">
         <v>139</v>
-      </c>
-      <c r="AZ12" t="s">
-        <v>140</v>
       </c>
       <c r="BA12">
         <v>10</v>
@@ -7868,7 +7875,7 @@
         <v>1.5</v>
       </c>
       <c r="BC12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD12">
         <v>20</v>
@@ -7877,31 +7884,31 @@
         <v>1.5</v>
       </c>
       <c r="BF12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BG12">
         <v>1.42</v>
       </c>
       <c r="BH12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI12">
         <v>1.42</v>
       </c>
       <c r="BJ12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK12">
         <v>1.42</v>
       </c>
       <c r="BL12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BM12">
         <v>1.42</v>
       </c>
       <c r="BN12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BO12">
         <v>1.42</v>
@@ -7916,22 +7923,22 @@
         <v>120</v>
       </c>
       <c r="BS12" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT12" t="s">
         <v>142</v>
       </c>
-      <c r="BT12" t="s">
-        <v>143</v>
-      </c>
       <c r="BU12" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV12" t="s">
         <v>137</v>
       </c>
-      <c r="BV12" t="s">
+      <c r="BW12" t="s">
         <v>138</v>
       </c>
-      <c r="BW12" t="s">
+      <c r="BX12" t="s">
         <v>139</v>
-      </c>
-      <c r="BX12" t="s">
-        <v>140</v>
       </c>
       <c r="BY12">
         <v>10</v>
@@ -7940,13 +7947,13 @@
         <v>1.5</v>
       </c>
       <c r="CA12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CB12">
         <v>1.42</v>
       </c>
       <c r="CC12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CD12">
         <v>1.42</v>
@@ -7982,22 +7989,22 @@
         <v>120</v>
       </c>
       <c r="CO12" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP12" t="s">
         <v>142</v>
       </c>
-      <c r="CP12" t="s">
-        <v>143</v>
-      </c>
       <c r="CQ12" t="s">
+        <v>136</v>
+      </c>
+      <c r="CR12" t="s">
         <v>137</v>
       </c>
-      <c r="CR12" t="s">
+      <c r="CS12" t="s">
         <v>138</v>
       </c>
-      <c r="CS12" t="s">
+      <c r="CT12" t="s">
         <v>139</v>
-      </c>
-      <c r="CT12" t="s">
-        <v>140</v>
       </c>
       <c r="CU12">
         <v>10</v>
@@ -8006,19 +8013,19 @@
         <v>1.5</v>
       </c>
       <c r="CW12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CX12">
         <v>1.42</v>
       </c>
       <c r="CY12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CZ12">
         <v>1.42</v>
       </c>
       <c r="DA12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="DB12">
         <v>128</v>
@@ -8060,19 +8067,19 @@
         <v>120</v>
       </c>
       <c r="DO12" t="s">
+        <v>141</v>
+      </c>
+      <c r="DP12" t="s">
         <v>142</v>
       </c>
-      <c r="DP12" t="s">
-        <v>143</v>
-      </c>
       <c r="DQ12" t="s">
+        <v>144</v>
+      </c>
+      <c r="DR12" t="s">
         <v>145</v>
       </c>
-      <c r="DR12" t="s">
+      <c r="DS12" t="s">
         <v>146</v>
-      </c>
-      <c r="DS12" t="s">
-        <v>147</v>
       </c>
       <c r="DT12" t="b">
         <v>1</v>
@@ -8108,16 +8115,16 @@
         <v>1.5</v>
       </c>
       <c r="EE12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="EF12" t="s">
+        <v>144</v>
+      </c>
+      <c r="EG12" t="s">
         <v>145</v>
       </c>
-      <c r="EG12" t="s">
+      <c r="EH12" t="s">
         <v>146</v>
-      </c>
-      <c r="EH12" t="s">
-        <v>147</v>
       </c>
       <c r="EI12" t="b">
         <v>0</v>
@@ -8153,16 +8160,16 @@
         <v>1.5</v>
       </c>
       <c r="ET12" t="s">
+        <v>147</v>
+      </c>
+      <c r="EU12" t="s">
         <v>148</v>
       </c>
-      <c r="EU12" t="s">
+      <c r="EV12" t="s">
         <v>149</v>
       </c>
-      <c r="EV12" t="s">
+      <c r="EW12" t="s">
         <v>150</v>
-      </c>
-      <c r="EW12" t="s">
-        <v>151</v>
       </c>
       <c r="EX12">
         <v>9.9999999999999995E-7</v>
@@ -8177,13 +8184,13 @@
         <v>25</v>
       </c>
       <c r="FB12" t="s">
+        <v>148</v>
+      </c>
+      <c r="FC12" t="s">
         <v>149</v>
       </c>
-      <c r="FC12" t="s">
+      <c r="FD12" t="s">
         <v>150</v>
-      </c>
-      <c r="FD12" t="s">
-        <v>151</v>
       </c>
       <c r="FE12">
         <v>9.9999999999999995E-7</v>
@@ -8198,16 +8205,16 @@
         <v>25</v>
       </c>
       <c r="FI12" t="s">
+        <v>151</v>
+      </c>
+      <c r="FJ12" t="s">
+        <v>145</v>
+      </c>
+      <c r="FK12" t="s">
         <v>152</v>
       </c>
-      <c r="FJ12" t="s">
-        <v>146</v>
-      </c>
-      <c r="FK12" t="s">
+      <c r="FL12" t="s">
         <v>153</v>
-      </c>
-      <c r="FL12" t="s">
-        <v>154</v>
       </c>
       <c r="FM12">
         <v>200</v>
@@ -8234,7 +8241,7 @@
         <v>20</v>
       </c>
       <c r="FU12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="FV12">
         <v>532</v>
@@ -8255,19 +8262,19 @@
         <v>75</v>
       </c>
       <c r="GB12" t="s">
+        <v>155</v>
+      </c>
+      <c r="GC12" t="s">
         <v>156</v>
       </c>
-      <c r="GC12" t="s">
+      <c r="GD12" t="s">
+        <v>145</v>
+      </c>
+      <c r="GE12" t="s">
         <v>157</v>
       </c>
-      <c r="GD12" t="s">
-        <v>146</v>
-      </c>
-      <c r="GE12" t="s">
+      <c r="GF12" t="s">
         <v>158</v>
-      </c>
-      <c r="GF12" t="s">
-        <v>159</v>
       </c>
       <c r="GG12">
         <v>25</v>
@@ -8285,7 +8292,7 @@
         <v>250</v>
       </c>
       <c r="GL12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="GM12">
         <v>0.2</v>
@@ -8297,7 +8304,7 @@
         <v>25</v>
       </c>
       <c r="GP12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="GQ12">
         <v>0.1</v>
@@ -8312,19 +8319,19 @@
         <v>150</v>
       </c>
       <c r="GU12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="GV12">
         <v>35</v>
       </c>
       <c r="GW12" t="s">
+        <v>160</v>
+      </c>
+      <c r="GX12" t="s">
         <v>161</v>
       </c>
-      <c r="GX12" t="s">
+      <c r="GY12" t="s">
         <v>162</v>
-      </c>
-      <c r="GY12" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:207" x14ac:dyDescent="0.3">
@@ -8350,8 +8357,9 @@
       <c r="G13" t="s">
         <v>130</v>
       </c>
-      <c r="H13" t="s">
-        <v>131</v>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>6.25</v>
       </c>
       <c r="I13">
         <v>0.16</v>
@@ -8363,19 +8371,19 @@
         <v>0.16</v>
       </c>
       <c r="L13" t="s">
+        <v>131</v>
+      </c>
+      <c r="M13" t="s">
         <v>132</v>
-      </c>
-      <c r="M13" t="s">
-        <v>133</v>
       </c>
       <c r="N13">
         <v>1</v>
       </c>
       <c r="O13" t="s">
+        <v>133</v>
+      </c>
+      <c r="P13" t="s">
         <v>134</v>
-      </c>
-      <c r="P13" t="s">
-        <v>135</v>
       </c>
       <c r="Q13">
         <v>31</v>
@@ -8384,7 +8392,7 @@
         <v>61</v>
       </c>
       <c r="S13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T13">
         <v>32</v>
@@ -8393,7 +8401,7 @@
         <v>62</v>
       </c>
       <c r="V13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W13">
         <v>180</v>
@@ -8402,7 +8410,7 @@
         <v>50</v>
       </c>
       <c r="Y13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z13">
         <v>31</v>
@@ -8411,7 +8419,7 @@
         <v>61</v>
       </c>
       <c r="AB13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC13">
         <v>32</v>
@@ -8423,16 +8431,16 @@
         <v>900</v>
       </c>
       <c r="AF13" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG13" t="s">
         <v>137</v>
       </c>
-      <c r="AG13" t="s">
+      <c r="AH13" t="s">
         <v>138</v>
       </c>
-      <c r="AH13" t="s">
+      <c r="AI13" t="s">
         <v>139</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>140</v>
       </c>
       <c r="AJ13">
         <v>10</v>
@@ -8441,7 +8449,7 @@
         <v>1.5</v>
       </c>
       <c r="AL13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AM13">
         <v>1.42</v>
@@ -8468,22 +8476,22 @@
         <v>120</v>
       </c>
       <c r="AU13" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV13" t="s">
         <v>142</v>
       </c>
-      <c r="AV13" t="s">
-        <v>143</v>
-      </c>
       <c r="AW13" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX13" t="s">
         <v>137</v>
       </c>
-      <c r="AX13" t="s">
+      <c r="AY13" t="s">
         <v>138</v>
       </c>
-      <c r="AY13" t="s">
+      <c r="AZ13" t="s">
         <v>139</v>
-      </c>
-      <c r="AZ13" t="s">
-        <v>140</v>
       </c>
       <c r="BA13">
         <v>10</v>
@@ -8492,7 +8500,7 @@
         <v>1.5</v>
       </c>
       <c r="BC13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD13">
         <v>20</v>
@@ -8501,31 +8509,31 @@
         <v>1.5</v>
       </c>
       <c r="BF13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BG13">
         <v>1.42</v>
       </c>
       <c r="BH13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI13">
         <v>1.42</v>
       </c>
       <c r="BJ13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK13">
         <v>1.42</v>
       </c>
       <c r="BL13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BM13">
         <v>1.42</v>
       </c>
       <c r="BN13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BO13">
         <v>1.42</v>
@@ -8540,22 +8548,22 @@
         <v>120</v>
       </c>
       <c r="BS13" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT13" t="s">
         <v>142</v>
       </c>
-      <c r="BT13" t="s">
-        <v>143</v>
-      </c>
       <c r="BU13" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV13" t="s">
         <v>137</v>
       </c>
-      <c r="BV13" t="s">
+      <c r="BW13" t="s">
         <v>138</v>
       </c>
-      <c r="BW13" t="s">
+      <c r="BX13" t="s">
         <v>139</v>
-      </c>
-      <c r="BX13" t="s">
-        <v>140</v>
       </c>
       <c r="BY13">
         <v>10</v>
@@ -8564,13 +8572,13 @@
         <v>1.5</v>
       </c>
       <c r="CA13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CB13">
         <v>1.42</v>
       </c>
       <c r="CC13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CD13">
         <v>1.42</v>
@@ -8606,22 +8614,22 @@
         <v>120</v>
       </c>
       <c r="CO13" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP13" t="s">
         <v>142</v>
       </c>
-      <c r="CP13" t="s">
-        <v>143</v>
-      </c>
       <c r="CQ13" t="s">
+        <v>136</v>
+      </c>
+      <c r="CR13" t="s">
         <v>137</v>
       </c>
-      <c r="CR13" t="s">
+      <c r="CS13" t="s">
         <v>138</v>
       </c>
-      <c r="CS13" t="s">
+      <c r="CT13" t="s">
         <v>139</v>
-      </c>
-      <c r="CT13" t="s">
-        <v>140</v>
       </c>
       <c r="CU13">
         <v>10</v>
@@ -8630,19 +8638,19 @@
         <v>1.5</v>
       </c>
       <c r="CW13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CX13">
         <v>1.42</v>
       </c>
       <c r="CY13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CZ13">
         <v>1.42</v>
       </c>
       <c r="DA13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="DB13">
         <v>128</v>
@@ -8684,19 +8692,19 @@
         <v>120</v>
       </c>
       <c r="DO13" t="s">
+        <v>141</v>
+      </c>
+      <c r="DP13" t="s">
         <v>142</v>
       </c>
-      <c r="DP13" t="s">
-        <v>143</v>
-      </c>
       <c r="DQ13" t="s">
+        <v>144</v>
+      </c>
+      <c r="DR13" t="s">
         <v>145</v>
       </c>
-      <c r="DR13" t="s">
+      <c r="DS13" t="s">
         <v>146</v>
-      </c>
-      <c r="DS13" t="s">
-        <v>147</v>
       </c>
       <c r="DT13" t="b">
         <v>1</v>
@@ -8732,16 +8740,16 @@
         <v>1.5</v>
       </c>
       <c r="EE13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="EF13" t="s">
+        <v>144</v>
+      </c>
+      <c r="EG13" t="s">
         <v>145</v>
       </c>
-      <c r="EG13" t="s">
+      <c r="EH13" t="s">
         <v>146</v>
-      </c>
-      <c r="EH13" t="s">
-        <v>147</v>
       </c>
       <c r="EI13" t="b">
         <v>0</v>
@@ -8777,16 +8785,16 @@
         <v>1.5</v>
       </c>
       <c r="ET13" t="s">
+        <v>147</v>
+      </c>
+      <c r="EU13" t="s">
         <v>148</v>
       </c>
-      <c r="EU13" t="s">
+      <c r="EV13" t="s">
         <v>149</v>
       </c>
-      <c r="EV13" t="s">
+      <c r="EW13" t="s">
         <v>150</v>
-      </c>
-      <c r="EW13" t="s">
-        <v>151</v>
       </c>
       <c r="EX13">
         <v>9.9999999999999995E-7</v>
@@ -8801,13 +8809,13 @@
         <v>25</v>
       </c>
       <c r="FB13" t="s">
+        <v>148</v>
+      </c>
+      <c r="FC13" t="s">
         <v>149</v>
       </c>
-      <c r="FC13" t="s">
+      <c r="FD13" t="s">
         <v>150</v>
-      </c>
-      <c r="FD13" t="s">
-        <v>151</v>
       </c>
       <c r="FE13">
         <v>9.9999999999999995E-7</v>
@@ -8822,16 +8830,16 @@
         <v>25</v>
       </c>
       <c r="FI13" t="s">
+        <v>151</v>
+      </c>
+      <c r="FJ13" t="s">
+        <v>145</v>
+      </c>
+      <c r="FK13" t="s">
         <v>152</v>
       </c>
-      <c r="FJ13" t="s">
-        <v>146</v>
-      </c>
-      <c r="FK13" t="s">
+      <c r="FL13" t="s">
         <v>153</v>
-      </c>
-      <c r="FL13" t="s">
-        <v>154</v>
       </c>
       <c r="FM13">
         <v>200</v>
@@ -8858,7 +8866,7 @@
         <v>20</v>
       </c>
       <c r="FU13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="FV13">
         <v>532</v>
@@ -8879,19 +8887,19 @@
         <v>75</v>
       </c>
       <c r="GB13" t="s">
+        <v>155</v>
+      </c>
+      <c r="GC13" t="s">
         <v>156</v>
       </c>
-      <c r="GC13" t="s">
+      <c r="GD13" t="s">
+        <v>145</v>
+      </c>
+      <c r="GE13" t="s">
         <v>157</v>
       </c>
-      <c r="GD13" t="s">
-        <v>146</v>
-      </c>
-      <c r="GE13" t="s">
+      <c r="GF13" t="s">
         <v>158</v>
-      </c>
-      <c r="GF13" t="s">
-        <v>159</v>
       </c>
       <c r="GG13">
         <v>25</v>
@@ -8909,7 +8917,7 @@
         <v>250</v>
       </c>
       <c r="GL13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="GM13">
         <v>0.2</v>
@@ -8921,7 +8929,7 @@
         <v>25</v>
       </c>
       <c r="GP13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="GQ13">
         <v>0.1</v>
@@ -8936,19 +8944,19 @@
         <v>150</v>
       </c>
       <c r="GU13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="GV13">
         <v>35</v>
       </c>
       <c r="GW13" t="s">
+        <v>160</v>
+      </c>
+      <c r="GX13" t="s">
         <v>161</v>
       </c>
-      <c r="GX13" t="s">
+      <c r="GY13" t="s">
         <v>162</v>
-      </c>
-      <c r="GY13" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:207" x14ac:dyDescent="0.3">
@@ -8974,8 +8982,9 @@
       <c r="G14" t="s">
         <v>130</v>
       </c>
-      <c r="H14" t="s">
-        <v>131</v>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>6.25</v>
       </c>
       <c r="I14">
         <v>0.16</v>
@@ -8987,19 +8996,19 @@
         <v>0.16</v>
       </c>
       <c r="L14" t="s">
+        <v>131</v>
+      </c>
+      <c r="M14" t="s">
         <v>132</v>
-      </c>
-      <c r="M14" t="s">
-        <v>133</v>
       </c>
       <c r="N14">
         <v>1</v>
       </c>
       <c r="O14" t="s">
+        <v>133</v>
+      </c>
+      <c r="P14" t="s">
         <v>134</v>
-      </c>
-      <c r="P14" t="s">
-        <v>135</v>
       </c>
       <c r="Q14">
         <v>31</v>
@@ -9008,7 +9017,7 @@
         <v>61</v>
       </c>
       <c r="S14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T14">
         <v>32</v>
@@ -9017,7 +9026,7 @@
         <v>62</v>
       </c>
       <c r="V14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W14">
         <v>180</v>
@@ -9026,7 +9035,7 @@
         <v>50</v>
       </c>
       <c r="Y14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z14">
         <v>31</v>
@@ -9035,7 +9044,7 @@
         <v>61</v>
       </c>
       <c r="AB14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC14">
         <v>32</v>
@@ -9047,16 +9056,16 @@
         <v>900</v>
       </c>
       <c r="AF14" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG14" t="s">
         <v>137</v>
       </c>
-      <c r="AG14" t="s">
+      <c r="AH14" t="s">
         <v>138</v>
       </c>
-      <c r="AH14" t="s">
+      <c r="AI14" t="s">
         <v>139</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>140</v>
       </c>
       <c r="AJ14">
         <v>10</v>
@@ -9065,7 +9074,7 @@
         <v>1.5</v>
       </c>
       <c r="AL14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AM14">
         <v>1.42</v>
@@ -9092,22 +9101,22 @@
         <v>120</v>
       </c>
       <c r="AU14" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV14" t="s">
         <v>142</v>
       </c>
-      <c r="AV14" t="s">
-        <v>143</v>
-      </c>
       <c r="AW14" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX14" t="s">
         <v>137</v>
       </c>
-      <c r="AX14" t="s">
+      <c r="AY14" t="s">
         <v>138</v>
       </c>
-      <c r="AY14" t="s">
+      <c r="AZ14" t="s">
         <v>139</v>
-      </c>
-      <c r="AZ14" t="s">
-        <v>140</v>
       </c>
       <c r="BA14">
         <v>10</v>
@@ -9116,7 +9125,7 @@
         <v>1.5</v>
       </c>
       <c r="BC14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD14">
         <v>20</v>
@@ -9125,31 +9134,31 @@
         <v>1.5</v>
       </c>
       <c r="BF14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BG14">
         <v>1.42</v>
       </c>
       <c r="BH14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI14">
         <v>1.42</v>
       </c>
       <c r="BJ14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK14">
         <v>1.42</v>
       </c>
       <c r="BL14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BM14">
         <v>1.42</v>
       </c>
       <c r="BN14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BO14">
         <v>1.42</v>
@@ -9164,22 +9173,22 @@
         <v>120</v>
       </c>
       <c r="BS14" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT14" t="s">
         <v>142</v>
       </c>
-      <c r="BT14" t="s">
-        <v>143</v>
-      </c>
       <c r="BU14" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV14" t="s">
         <v>137</v>
       </c>
-      <c r="BV14" t="s">
+      <c r="BW14" t="s">
         <v>138</v>
       </c>
-      <c r="BW14" t="s">
+      <c r="BX14" t="s">
         <v>139</v>
-      </c>
-      <c r="BX14" t="s">
-        <v>140</v>
       </c>
       <c r="BY14">
         <v>10</v>
@@ -9188,13 +9197,13 @@
         <v>1.5</v>
       </c>
       <c r="CA14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CB14">
         <v>1.42</v>
       </c>
       <c r="CC14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CD14">
         <v>1.42</v>
@@ -9230,22 +9239,22 @@
         <v>120</v>
       </c>
       <c r="CO14" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP14" t="s">
         <v>142</v>
       </c>
-      <c r="CP14" t="s">
-        <v>143</v>
-      </c>
       <c r="CQ14" t="s">
+        <v>136</v>
+      </c>
+      <c r="CR14" t="s">
         <v>137</v>
       </c>
-      <c r="CR14" t="s">
+      <c r="CS14" t="s">
         <v>138</v>
       </c>
-      <c r="CS14" t="s">
+      <c r="CT14" t="s">
         <v>139</v>
-      </c>
-      <c r="CT14" t="s">
-        <v>140</v>
       </c>
       <c r="CU14">
         <v>10</v>
@@ -9254,19 +9263,19 @@
         <v>1.5</v>
       </c>
       <c r="CW14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CX14">
         <v>1.42</v>
       </c>
       <c r="CY14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CZ14">
         <v>1.42</v>
       </c>
       <c r="DA14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="DB14">
         <v>128</v>
@@ -9308,19 +9317,19 @@
         <v>120</v>
       </c>
       <c r="DO14" t="s">
+        <v>141</v>
+      </c>
+      <c r="DP14" t="s">
         <v>142</v>
       </c>
-      <c r="DP14" t="s">
-        <v>143</v>
-      </c>
       <c r="DQ14" t="s">
+        <v>144</v>
+      </c>
+      <c r="DR14" t="s">
         <v>145</v>
       </c>
-      <c r="DR14" t="s">
+      <c r="DS14" t="s">
         <v>146</v>
-      </c>
-      <c r="DS14" t="s">
-        <v>147</v>
       </c>
       <c r="DT14" t="b">
         <v>1</v>
@@ -9356,16 +9365,16 @@
         <v>1.5</v>
       </c>
       <c r="EE14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="EF14" t="s">
+        <v>144</v>
+      </c>
+      <c r="EG14" t="s">
         <v>145</v>
       </c>
-      <c r="EG14" t="s">
+      <c r="EH14" t="s">
         <v>146</v>
-      </c>
-      <c r="EH14" t="s">
-        <v>147</v>
       </c>
       <c r="EI14" t="b">
         <v>0</v>
@@ -9401,16 +9410,16 @@
         <v>1.5</v>
       </c>
       <c r="ET14" t="s">
+        <v>147</v>
+      </c>
+      <c r="EU14" t="s">
         <v>148</v>
       </c>
-      <c r="EU14" t="s">
+      <c r="EV14" t="s">
         <v>149</v>
       </c>
-      <c r="EV14" t="s">
+      <c r="EW14" t="s">
         <v>150</v>
-      </c>
-      <c r="EW14" t="s">
-        <v>151</v>
       </c>
       <c r="EX14">
         <v>9.9999999999999995E-7</v>
@@ -9425,13 +9434,13 @@
         <v>25</v>
       </c>
       <c r="FB14" t="s">
+        <v>148</v>
+      </c>
+      <c r="FC14" t="s">
         <v>149</v>
       </c>
-      <c r="FC14" t="s">
+      <c r="FD14" t="s">
         <v>150</v>
-      </c>
-      <c r="FD14" t="s">
-        <v>151</v>
       </c>
       <c r="FE14">
         <v>9.9999999999999995E-7</v>
@@ -9446,16 +9455,16 @@
         <v>25</v>
       </c>
       <c r="FI14" t="s">
+        <v>151</v>
+      </c>
+      <c r="FJ14" t="s">
+        <v>145</v>
+      </c>
+      <c r="FK14" t="s">
         <v>152</v>
       </c>
-      <c r="FJ14" t="s">
-        <v>146</v>
-      </c>
-      <c r="FK14" t="s">
+      <c r="FL14" t="s">
         <v>153</v>
-      </c>
-      <c r="FL14" t="s">
-        <v>154</v>
       </c>
       <c r="FM14">
         <v>200</v>
@@ -9482,7 +9491,7 @@
         <v>20</v>
       </c>
       <c r="FU14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="FV14">
         <v>532</v>
@@ -9503,19 +9512,19 @@
         <v>75</v>
       </c>
       <c r="GB14" t="s">
+        <v>155</v>
+      </c>
+      <c r="GC14" t="s">
         <v>156</v>
       </c>
-      <c r="GC14" t="s">
+      <c r="GD14" t="s">
+        <v>145</v>
+      </c>
+      <c r="GE14" t="s">
         <v>157</v>
       </c>
-      <c r="GD14" t="s">
-        <v>146</v>
-      </c>
-      <c r="GE14" t="s">
+      <c r="GF14" t="s">
         <v>158</v>
-      </c>
-      <c r="GF14" t="s">
-        <v>159</v>
       </c>
       <c r="GG14">
         <v>25</v>
@@ -9533,7 +9542,7 @@
         <v>250</v>
       </c>
       <c r="GL14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="GM14">
         <v>0.2</v>
@@ -9545,7 +9554,7 @@
         <v>25</v>
       </c>
       <c r="GP14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="GQ14">
         <v>0.1</v>
@@ -9560,19 +9569,19 @@
         <v>150</v>
       </c>
       <c r="GU14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="GV14">
         <v>35</v>
       </c>
       <c r="GW14" t="s">
+        <v>160</v>
+      </c>
+      <c r="GX14" t="s">
         <v>161</v>
       </c>
-      <c r="GX14" t="s">
+      <c r="GY14" t="s">
         <v>162</v>
-      </c>
-      <c r="GY14" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:207" x14ac:dyDescent="0.3">
@@ -9598,8 +9607,9 @@
       <c r="G15" t="s">
         <v>130</v>
       </c>
-      <c r="H15" t="s">
-        <v>131</v>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>6.25</v>
       </c>
       <c r="I15">
         <v>0.16</v>
@@ -9611,19 +9621,19 @@
         <v>0.16</v>
       </c>
       <c r="L15" t="s">
+        <v>131</v>
+      </c>
+      <c r="M15" t="s">
         <v>132</v>
-      </c>
-      <c r="M15" t="s">
-        <v>133</v>
       </c>
       <c r="N15">
         <v>1</v>
       </c>
       <c r="O15" t="s">
+        <v>133</v>
+      </c>
+      <c r="P15" t="s">
         <v>134</v>
-      </c>
-      <c r="P15" t="s">
-        <v>135</v>
       </c>
       <c r="Q15">
         <v>31</v>
@@ -9632,7 +9642,7 @@
         <v>61</v>
       </c>
       <c r="S15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T15">
         <v>32</v>
@@ -9641,7 +9651,7 @@
         <v>62</v>
       </c>
       <c r="V15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W15">
         <v>180</v>
@@ -9650,7 +9660,7 @@
         <v>50</v>
       </c>
       <c r="Y15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z15">
         <v>31</v>
@@ -9659,7 +9669,7 @@
         <v>61</v>
       </c>
       <c r="AB15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC15">
         <v>32</v>
@@ -9671,16 +9681,16 @@
         <v>900</v>
       </c>
       <c r="AF15" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG15" t="s">
         <v>137</v>
       </c>
-      <c r="AG15" t="s">
+      <c r="AH15" t="s">
         <v>138</v>
       </c>
-      <c r="AH15" t="s">
+      <c r="AI15" t="s">
         <v>139</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>140</v>
       </c>
       <c r="AJ15">
         <v>10</v>
@@ -9689,7 +9699,7 @@
         <v>1.5</v>
       </c>
       <c r="AL15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AM15">
         <v>1.42</v>
@@ -9716,22 +9726,22 @@
         <v>120</v>
       </c>
       <c r="AU15" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV15" t="s">
         <v>142</v>
       </c>
-      <c r="AV15" t="s">
-        <v>143</v>
-      </c>
       <c r="AW15" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX15" t="s">
         <v>137</v>
       </c>
-      <c r="AX15" t="s">
+      <c r="AY15" t="s">
         <v>138</v>
       </c>
-      <c r="AY15" t="s">
+      <c r="AZ15" t="s">
         <v>139</v>
-      </c>
-      <c r="AZ15" t="s">
-        <v>140</v>
       </c>
       <c r="BA15">
         <v>10</v>
@@ -9740,7 +9750,7 @@
         <v>1.5</v>
       </c>
       <c r="BC15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD15">
         <v>20</v>
@@ -9749,31 +9759,31 @@
         <v>1.5</v>
       </c>
       <c r="BF15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BG15">
         <v>1.42</v>
       </c>
       <c r="BH15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI15">
         <v>1.42</v>
       </c>
       <c r="BJ15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK15">
         <v>1.42</v>
       </c>
       <c r="BL15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BM15">
         <v>1.42</v>
       </c>
       <c r="BN15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BO15">
         <v>1.42</v>
@@ -9788,22 +9798,22 @@
         <v>120</v>
       </c>
       <c r="BS15" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT15" t="s">
         <v>142</v>
       </c>
-      <c r="BT15" t="s">
-        <v>143</v>
-      </c>
       <c r="BU15" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV15" t="s">
         <v>137</v>
       </c>
-      <c r="BV15" t="s">
+      <c r="BW15" t="s">
         <v>138</v>
       </c>
-      <c r="BW15" t="s">
+      <c r="BX15" t="s">
         <v>139</v>
-      </c>
-      <c r="BX15" t="s">
-        <v>140</v>
       </c>
       <c r="BY15">
         <v>10</v>
@@ -9812,13 +9822,13 @@
         <v>1.5</v>
       </c>
       <c r="CA15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CB15">
         <v>1.42</v>
       </c>
       <c r="CC15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CD15">
         <v>1.42</v>
@@ -9854,22 +9864,22 @@
         <v>120</v>
       </c>
       <c r="CO15" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP15" t="s">
         <v>142</v>
       </c>
-      <c r="CP15" t="s">
-        <v>143</v>
-      </c>
       <c r="CQ15" t="s">
+        <v>136</v>
+      </c>
+      <c r="CR15" t="s">
         <v>137</v>
       </c>
-      <c r="CR15" t="s">
+      <c r="CS15" t="s">
         <v>138</v>
       </c>
-      <c r="CS15" t="s">
+      <c r="CT15" t="s">
         <v>139</v>
-      </c>
-      <c r="CT15" t="s">
-        <v>140</v>
       </c>
       <c r="CU15">
         <v>10</v>
@@ -9878,19 +9888,19 @@
         <v>1.5</v>
       </c>
       <c r="CW15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CX15">
         <v>1.42</v>
       </c>
       <c r="CY15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CZ15">
         <v>1.42</v>
       </c>
       <c r="DA15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="DB15">
         <v>128</v>
@@ -9932,19 +9942,19 @@
         <v>120</v>
       </c>
       <c r="DO15" t="s">
+        <v>141</v>
+      </c>
+      <c r="DP15" t="s">
         <v>142</v>
       </c>
-      <c r="DP15" t="s">
-        <v>143</v>
-      </c>
       <c r="DQ15" t="s">
+        <v>144</v>
+      </c>
+      <c r="DR15" t="s">
         <v>145</v>
       </c>
-      <c r="DR15" t="s">
+      <c r="DS15" t="s">
         <v>146</v>
-      </c>
-      <c r="DS15" t="s">
-        <v>147</v>
       </c>
       <c r="DT15" t="b">
         <v>1</v>
@@ -9980,16 +9990,16 @@
         <v>1.5</v>
       </c>
       <c r="EE15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="EF15" t="s">
+        <v>144</v>
+      </c>
+      <c r="EG15" t="s">
         <v>145</v>
       </c>
-      <c r="EG15" t="s">
+      <c r="EH15" t="s">
         <v>146</v>
-      </c>
-      <c r="EH15" t="s">
-        <v>147</v>
       </c>
       <c r="EI15" t="b">
         <v>0</v>
@@ -10025,16 +10035,16 @@
         <v>1.5</v>
       </c>
       <c r="ET15" t="s">
+        <v>147</v>
+      </c>
+      <c r="EU15" t="s">
         <v>148</v>
       </c>
-      <c r="EU15" t="s">
+      <c r="EV15" t="s">
         <v>149</v>
       </c>
-      <c r="EV15" t="s">
+      <c r="EW15" t="s">
         <v>150</v>
-      </c>
-      <c r="EW15" t="s">
-        <v>151</v>
       </c>
       <c r="EX15">
         <v>9.9999999999999995E-7</v>
@@ -10049,13 +10059,13 @@
         <v>25</v>
       </c>
       <c r="FB15" t="s">
+        <v>148</v>
+      </c>
+      <c r="FC15" t="s">
         <v>149</v>
       </c>
-      <c r="FC15" t="s">
+      <c r="FD15" t="s">
         <v>150</v>
-      </c>
-      <c r="FD15" t="s">
-        <v>151</v>
       </c>
       <c r="FE15">
         <v>9.9999999999999995E-7</v>
@@ -10070,16 +10080,16 @@
         <v>25</v>
       </c>
       <c r="FI15" t="s">
+        <v>151</v>
+      </c>
+      <c r="FJ15" t="s">
+        <v>145</v>
+      </c>
+      <c r="FK15" t="s">
         <v>152</v>
       </c>
-      <c r="FJ15" t="s">
-        <v>146</v>
-      </c>
-      <c r="FK15" t="s">
+      <c r="FL15" t="s">
         <v>153</v>
-      </c>
-      <c r="FL15" t="s">
-        <v>154</v>
       </c>
       <c r="FM15">
         <v>200</v>
@@ -10106,7 +10116,7 @@
         <v>20</v>
       </c>
       <c r="FU15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="FV15">
         <v>532</v>
@@ -10127,19 +10137,19 @@
         <v>75</v>
       </c>
       <c r="GB15" t="s">
+        <v>155</v>
+      </c>
+      <c r="GC15" t="s">
         <v>156</v>
       </c>
-      <c r="GC15" t="s">
+      <c r="GD15" t="s">
+        <v>145</v>
+      </c>
+      <c r="GE15" t="s">
         <v>157</v>
       </c>
-      <c r="GD15" t="s">
-        <v>146</v>
-      </c>
-      <c r="GE15" t="s">
+      <c r="GF15" t="s">
         <v>158</v>
-      </c>
-      <c r="GF15" t="s">
-        <v>159</v>
       </c>
       <c r="GG15">
         <v>25</v>
@@ -10157,7 +10167,7 @@
         <v>250</v>
       </c>
       <c r="GL15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="GM15">
         <v>0.2</v>
@@ -10169,7 +10179,7 @@
         <v>25</v>
       </c>
       <c r="GP15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="GQ15">
         <v>0.1</v>
@@ -10184,19 +10194,19 @@
         <v>150</v>
       </c>
       <c r="GU15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="GV15">
         <v>35</v>
       </c>
       <c r="GW15" t="s">
+        <v>160</v>
+      </c>
+      <c r="GX15" t="s">
         <v>161</v>
       </c>
-      <c r="GX15" t="s">
+      <c r="GY15" t="s">
         <v>162</v>
-      </c>
-      <c r="GY15" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:207" x14ac:dyDescent="0.3">
@@ -10222,8 +10232,9 @@
       <c r="G16" t="s">
         <v>130</v>
       </c>
-      <c r="H16" t="s">
-        <v>131</v>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>6.25</v>
       </c>
       <c r="I16">
         <v>0.16</v>
@@ -10235,19 +10246,19 @@
         <v>0.16</v>
       </c>
       <c r="L16" t="s">
+        <v>131</v>
+      </c>
+      <c r="M16" t="s">
         <v>132</v>
-      </c>
-      <c r="M16" t="s">
-        <v>133</v>
       </c>
       <c r="N16">
         <v>1</v>
       </c>
       <c r="O16" t="s">
+        <v>133</v>
+      </c>
+      <c r="P16" t="s">
         <v>134</v>
-      </c>
-      <c r="P16" t="s">
-        <v>135</v>
       </c>
       <c r="Q16">
         <v>31</v>
@@ -10256,7 +10267,7 @@
         <v>61</v>
       </c>
       <c r="S16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T16">
         <v>32</v>
@@ -10265,7 +10276,7 @@
         <v>62</v>
       </c>
       <c r="V16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W16">
         <v>180</v>
@@ -10274,7 +10285,7 @@
         <v>50</v>
       </c>
       <c r="Y16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z16">
         <v>31</v>
@@ -10283,7 +10294,7 @@
         <v>61</v>
       </c>
       <c r="AB16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC16">
         <v>32</v>
@@ -10295,16 +10306,16 @@
         <v>900</v>
       </c>
       <c r="AF16" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG16" t="s">
         <v>137</v>
       </c>
-      <c r="AG16" t="s">
+      <c r="AH16" t="s">
         <v>138</v>
       </c>
-      <c r="AH16" t="s">
+      <c r="AI16" t="s">
         <v>139</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>140</v>
       </c>
       <c r="AJ16">
         <v>10</v>
@@ -10313,7 +10324,7 @@
         <v>1.5</v>
       </c>
       <c r="AL16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AM16">
         <v>1.42</v>
@@ -10340,22 +10351,22 @@
         <v>120</v>
       </c>
       <c r="AU16" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV16" t="s">
         <v>142</v>
       </c>
-      <c r="AV16" t="s">
-        <v>143</v>
-      </c>
       <c r="AW16" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX16" t="s">
         <v>137</v>
       </c>
-      <c r="AX16" t="s">
+      <c r="AY16" t="s">
         <v>138</v>
       </c>
-      <c r="AY16" t="s">
+      <c r="AZ16" t="s">
         <v>139</v>
-      </c>
-      <c r="AZ16" t="s">
-        <v>140</v>
       </c>
       <c r="BA16">
         <v>10</v>
@@ -10364,7 +10375,7 @@
         <v>1.5</v>
       </c>
       <c r="BC16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD16">
         <v>20</v>
@@ -10373,31 +10384,31 @@
         <v>1.5</v>
       </c>
       <c r="BF16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BG16">
         <v>1.42</v>
       </c>
       <c r="BH16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI16">
         <v>1.42</v>
       </c>
       <c r="BJ16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK16">
         <v>1.42</v>
       </c>
       <c r="BL16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BM16">
         <v>1.42</v>
       </c>
       <c r="BN16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BO16">
         <v>1.42</v>
@@ -10412,22 +10423,22 @@
         <v>120</v>
       </c>
       <c r="BS16" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT16" t="s">
         <v>142</v>
       </c>
-      <c r="BT16" t="s">
-        <v>143</v>
-      </c>
       <c r="BU16" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV16" t="s">
         <v>137</v>
       </c>
-      <c r="BV16" t="s">
+      <c r="BW16" t="s">
         <v>138</v>
       </c>
-      <c r="BW16" t="s">
+      <c r="BX16" t="s">
         <v>139</v>
-      </c>
-      <c r="BX16" t="s">
-        <v>140</v>
       </c>
       <c r="BY16">
         <v>10</v>
@@ -10436,13 +10447,13 @@
         <v>1.5</v>
       </c>
       <c r="CA16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CB16">
         <v>1.42</v>
       </c>
       <c r="CC16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CD16">
         <v>1.42</v>
@@ -10478,22 +10489,22 @@
         <v>120</v>
       </c>
       <c r="CO16" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP16" t="s">
         <v>142</v>
       </c>
-      <c r="CP16" t="s">
-        <v>143</v>
-      </c>
       <c r="CQ16" t="s">
+        <v>136</v>
+      </c>
+      <c r="CR16" t="s">
         <v>137</v>
       </c>
-      <c r="CR16" t="s">
+      <c r="CS16" t="s">
         <v>138</v>
       </c>
-      <c r="CS16" t="s">
+      <c r="CT16" t="s">
         <v>139</v>
-      </c>
-      <c r="CT16" t="s">
-        <v>140</v>
       </c>
       <c r="CU16">
         <v>10</v>
@@ -10502,19 +10513,19 @@
         <v>1.5</v>
       </c>
       <c r="CW16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CX16">
         <v>1.42</v>
       </c>
       <c r="CY16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CZ16">
         <v>1.42</v>
       </c>
       <c r="DA16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="DB16">
         <v>128</v>
@@ -10556,19 +10567,19 @@
         <v>120</v>
       </c>
       <c r="DO16" t="s">
+        <v>141</v>
+      </c>
+      <c r="DP16" t="s">
         <v>142</v>
       </c>
-      <c r="DP16" t="s">
-        <v>143</v>
-      </c>
       <c r="DQ16" t="s">
+        <v>144</v>
+      </c>
+      <c r="DR16" t="s">
         <v>145</v>
       </c>
-      <c r="DR16" t="s">
+      <c r="DS16" t="s">
         <v>146</v>
-      </c>
-      <c r="DS16" t="s">
-        <v>147</v>
       </c>
       <c r="DT16" t="b">
         <v>1</v>
@@ -10604,16 +10615,16 @@
         <v>1.5</v>
       </c>
       <c r="EE16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="EF16" t="s">
+        <v>144</v>
+      </c>
+      <c r="EG16" t="s">
         <v>145</v>
       </c>
-      <c r="EG16" t="s">
+      <c r="EH16" t="s">
         <v>146</v>
-      </c>
-      <c r="EH16" t="s">
-        <v>147</v>
       </c>
       <c r="EI16" t="b">
         <v>0</v>
@@ -10649,16 +10660,16 @@
         <v>1.5</v>
       </c>
       <c r="ET16" t="s">
+        <v>147</v>
+      </c>
+      <c r="EU16" t="s">
         <v>148</v>
       </c>
-      <c r="EU16" t="s">
+      <c r="EV16" t="s">
         <v>149</v>
       </c>
-      <c r="EV16" t="s">
+      <c r="EW16" t="s">
         <v>150</v>
-      </c>
-      <c r="EW16" t="s">
-        <v>151</v>
       </c>
       <c r="EX16">
         <v>9.9999999999999995E-7</v>
@@ -10673,13 +10684,13 @@
         <v>25</v>
       </c>
       <c r="FB16" t="s">
+        <v>148</v>
+      </c>
+      <c r="FC16" t="s">
         <v>149</v>
       </c>
-      <c r="FC16" t="s">
+      <c r="FD16" t="s">
         <v>150</v>
-      </c>
-      <c r="FD16" t="s">
-        <v>151</v>
       </c>
       <c r="FE16">
         <v>9.9999999999999995E-7</v>
@@ -10694,16 +10705,16 @@
         <v>25</v>
       </c>
       <c r="FI16" t="s">
+        <v>151</v>
+      </c>
+      <c r="FJ16" t="s">
+        <v>145</v>
+      </c>
+      <c r="FK16" t="s">
         <v>152</v>
       </c>
-      <c r="FJ16" t="s">
-        <v>146</v>
-      </c>
-      <c r="FK16" t="s">
+      <c r="FL16" t="s">
         <v>153</v>
-      </c>
-      <c r="FL16" t="s">
-        <v>154</v>
       </c>
       <c r="FM16">
         <v>200</v>
@@ -10730,7 +10741,7 @@
         <v>20</v>
       </c>
       <c r="FU16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="FV16">
         <v>532</v>
@@ -10751,19 +10762,19 @@
         <v>75</v>
       </c>
       <c r="GB16" t="s">
+        <v>155</v>
+      </c>
+      <c r="GC16" t="s">
         <v>156</v>
       </c>
-      <c r="GC16" t="s">
+      <c r="GD16" t="s">
+        <v>145</v>
+      </c>
+      <c r="GE16" t="s">
         <v>157</v>
       </c>
-      <c r="GD16" t="s">
-        <v>146</v>
-      </c>
-      <c r="GE16" t="s">
+      <c r="GF16" t="s">
         <v>158</v>
-      </c>
-      <c r="GF16" t="s">
-        <v>159</v>
       </c>
       <c r="GG16">
         <v>25</v>
@@ -10781,7 +10792,7 @@
         <v>250</v>
       </c>
       <c r="GL16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="GM16">
         <v>0.2</v>
@@ -10793,7 +10804,7 @@
         <v>25</v>
       </c>
       <c r="GP16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="GQ16">
         <v>0.1</v>
@@ -10808,19 +10819,19 @@
         <v>150</v>
       </c>
       <c r="GU16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="GV16">
         <v>35</v>
       </c>
       <c r="GW16" t="s">
+        <v>160</v>
+      </c>
+      <c r="GX16" t="s">
         <v>161</v>
       </c>
-      <c r="GX16" t="s">
+      <c r="GY16" t="s">
         <v>162</v>
-      </c>
-      <c r="GY16" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:207" x14ac:dyDescent="0.3">
@@ -10846,8 +10857,9 @@
       <c r="G17" t="s">
         <v>130</v>
       </c>
-      <c r="H17" t="s">
-        <v>131</v>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>6.25</v>
       </c>
       <c r="I17">
         <v>0.16</v>
@@ -10859,19 +10871,19 @@
         <v>0.16</v>
       </c>
       <c r="L17" t="s">
+        <v>131</v>
+      </c>
+      <c r="M17" t="s">
         <v>132</v>
-      </c>
-      <c r="M17" t="s">
-        <v>133</v>
       </c>
       <c r="N17">
         <v>1</v>
       </c>
       <c r="O17" t="s">
+        <v>133</v>
+      </c>
+      <c r="P17" t="s">
         <v>134</v>
-      </c>
-      <c r="P17" t="s">
-        <v>135</v>
       </c>
       <c r="Q17">
         <v>31</v>
@@ -10880,7 +10892,7 @@
         <v>61</v>
       </c>
       <c r="S17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T17">
         <v>32</v>
@@ -10889,7 +10901,7 @@
         <v>62</v>
       </c>
       <c r="V17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W17">
         <v>180</v>
@@ -10898,7 +10910,7 @@
         <v>50</v>
       </c>
       <c r="Y17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z17">
         <v>31</v>
@@ -10907,7 +10919,7 @@
         <v>61</v>
       </c>
       <c r="AB17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC17">
         <v>32</v>
@@ -10919,16 +10931,16 @@
         <v>900</v>
       </c>
       <c r="AF17" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG17" t="s">
         <v>137</v>
       </c>
-      <c r="AG17" t="s">
+      <c r="AH17" t="s">
         <v>138</v>
       </c>
-      <c r="AH17" t="s">
+      <c r="AI17" t="s">
         <v>139</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>140</v>
       </c>
       <c r="AJ17">
         <v>10</v>
@@ -10937,7 +10949,7 @@
         <v>1.5</v>
       </c>
       <c r="AL17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AM17">
         <v>1.42</v>
@@ -10964,22 +10976,22 @@
         <v>120</v>
       </c>
       <c r="AU17" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV17" t="s">
         <v>142</v>
       </c>
-      <c r="AV17" t="s">
-        <v>143</v>
-      </c>
       <c r="AW17" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX17" t="s">
         <v>137</v>
       </c>
-      <c r="AX17" t="s">
+      <c r="AY17" t="s">
         <v>138</v>
       </c>
-      <c r="AY17" t="s">
+      <c r="AZ17" t="s">
         <v>139</v>
-      </c>
-      <c r="AZ17" t="s">
-        <v>140</v>
       </c>
       <c r="BA17">
         <v>10</v>
@@ -10988,7 +11000,7 @@
         <v>1.5</v>
       </c>
       <c r="BC17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD17">
         <v>20</v>
@@ -10997,31 +11009,31 @@
         <v>1.5</v>
       </c>
       <c r="BF17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BG17">
         <v>1.42</v>
       </c>
       <c r="BH17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI17">
         <v>1.42</v>
       </c>
       <c r="BJ17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK17">
         <v>1.42</v>
       </c>
       <c r="BL17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BM17">
         <v>1.42</v>
       </c>
       <c r="BN17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BO17">
         <v>1.42</v>
@@ -11036,22 +11048,22 @@
         <v>120</v>
       </c>
       <c r="BS17" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT17" t="s">
         <v>142</v>
       </c>
-      <c r="BT17" t="s">
-        <v>143</v>
-      </c>
       <c r="BU17" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV17" t="s">
         <v>137</v>
       </c>
-      <c r="BV17" t="s">
+      <c r="BW17" t="s">
         <v>138</v>
       </c>
-      <c r="BW17" t="s">
+      <c r="BX17" t="s">
         <v>139</v>
-      </c>
-      <c r="BX17" t="s">
-        <v>140</v>
       </c>
       <c r="BY17">
         <v>10</v>
@@ -11060,13 +11072,13 @@
         <v>1.5</v>
       </c>
       <c r="CA17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CB17">
         <v>1.42</v>
       </c>
       <c r="CC17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CD17">
         <v>1.42</v>
@@ -11102,22 +11114,22 @@
         <v>120</v>
       </c>
       <c r="CO17" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP17" t="s">
         <v>142</v>
       </c>
-      <c r="CP17" t="s">
-        <v>143</v>
-      </c>
       <c r="CQ17" t="s">
+        <v>136</v>
+      </c>
+      <c r="CR17" t="s">
         <v>137</v>
       </c>
-      <c r="CR17" t="s">
+      <c r="CS17" t="s">
         <v>138</v>
       </c>
-      <c r="CS17" t="s">
+      <c r="CT17" t="s">
         <v>139</v>
-      </c>
-      <c r="CT17" t="s">
-        <v>140</v>
       </c>
       <c r="CU17">
         <v>10</v>
@@ -11126,19 +11138,19 @@
         <v>1.5</v>
       </c>
       <c r="CW17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CX17">
         <v>1.42</v>
       </c>
       <c r="CY17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CZ17">
         <v>1.42</v>
       </c>
       <c r="DA17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="DB17">
         <v>128</v>
@@ -11180,19 +11192,19 @@
         <v>120</v>
       </c>
       <c r="DO17" t="s">
+        <v>141</v>
+      </c>
+      <c r="DP17" t="s">
         <v>142</v>
       </c>
-      <c r="DP17" t="s">
-        <v>143</v>
-      </c>
       <c r="DQ17" t="s">
+        <v>144</v>
+      </c>
+      <c r="DR17" t="s">
         <v>145</v>
       </c>
-      <c r="DR17" t="s">
+      <c r="DS17" t="s">
         <v>146</v>
-      </c>
-      <c r="DS17" t="s">
-        <v>147</v>
       </c>
       <c r="DT17" t="b">
         <v>1</v>
@@ -11228,16 +11240,16 @@
         <v>1.5</v>
       </c>
       <c r="EE17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="EF17" t="s">
+        <v>144</v>
+      </c>
+      <c r="EG17" t="s">
         <v>145</v>
       </c>
-      <c r="EG17" t="s">
+      <c r="EH17" t="s">
         <v>146</v>
-      </c>
-      <c r="EH17" t="s">
-        <v>147</v>
       </c>
       <c r="EI17" t="b">
         <v>0</v>
@@ -11273,16 +11285,16 @@
         <v>1.5</v>
       </c>
       <c r="ET17" t="s">
+        <v>147</v>
+      </c>
+      <c r="EU17" t="s">
         <v>148</v>
       </c>
-      <c r="EU17" t="s">
+      <c r="EV17" t="s">
         <v>149</v>
       </c>
-      <c r="EV17" t="s">
+      <c r="EW17" t="s">
         <v>150</v>
-      </c>
-      <c r="EW17" t="s">
-        <v>151</v>
       </c>
       <c r="EX17">
         <v>9.9999999999999995E-7</v>
@@ -11297,13 +11309,13 @@
         <v>25</v>
       </c>
       <c r="FB17" t="s">
+        <v>148</v>
+      </c>
+      <c r="FC17" t="s">
         <v>149</v>
       </c>
-      <c r="FC17" t="s">
+      <c r="FD17" t="s">
         <v>150</v>
-      </c>
-      <c r="FD17" t="s">
-        <v>151</v>
       </c>
       <c r="FE17">
         <v>9.9999999999999995E-7</v>
@@ -11318,16 +11330,16 @@
         <v>25</v>
       </c>
       <c r="FI17" t="s">
+        <v>151</v>
+      </c>
+      <c r="FJ17" t="s">
+        <v>145</v>
+      </c>
+      <c r="FK17" t="s">
         <v>152</v>
       </c>
-      <c r="FJ17" t="s">
-        <v>146</v>
-      </c>
-      <c r="FK17" t="s">
+      <c r="FL17" t="s">
         <v>153</v>
-      </c>
-      <c r="FL17" t="s">
-        <v>154</v>
       </c>
       <c r="FM17">
         <v>200</v>
@@ -11354,7 +11366,7 @@
         <v>20</v>
       </c>
       <c r="FU17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="FV17">
         <v>532</v>
@@ -11375,19 +11387,19 @@
         <v>75</v>
       </c>
       <c r="GB17" t="s">
+        <v>155</v>
+      </c>
+      <c r="GC17" t="s">
         <v>156</v>
       </c>
-      <c r="GC17" t="s">
+      <c r="GD17" t="s">
+        <v>145</v>
+      </c>
+      <c r="GE17" t="s">
         <v>157</v>
       </c>
-      <c r="GD17" t="s">
-        <v>146</v>
-      </c>
-      <c r="GE17" t="s">
+      <c r="GF17" t="s">
         <v>158</v>
-      </c>
-      <c r="GF17" t="s">
-        <v>159</v>
       </c>
       <c r="GG17">
         <v>25</v>
@@ -11405,7 +11417,7 @@
         <v>250</v>
       </c>
       <c r="GL17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="GM17">
         <v>0.2</v>
@@ -11417,7 +11429,7 @@
         <v>25</v>
       </c>
       <c r="GP17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="GQ17">
         <v>0.1</v>
@@ -11432,19 +11444,19 @@
         <v>150</v>
       </c>
       <c r="GU17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="GV17">
         <v>35</v>
       </c>
       <c r="GW17" t="s">
+        <v>160</v>
+      </c>
+      <c r="GX17" t="s">
         <v>161</v>
       </c>
-      <c r="GX17" t="s">
+      <c r="GY17" t="s">
         <v>162</v>
-      </c>
-      <c r="GY17" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:207" x14ac:dyDescent="0.3">
@@ -11470,8 +11482,9 @@
       <c r="G18" t="s">
         <v>130</v>
       </c>
-      <c r="H18" t="s">
-        <v>131</v>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>6.25</v>
       </c>
       <c r="I18">
         <v>0.16</v>
@@ -11483,19 +11496,19 @@
         <v>0.16</v>
       </c>
       <c r="L18" t="s">
+        <v>131</v>
+      </c>
+      <c r="M18" t="s">
         <v>132</v>
-      </c>
-      <c r="M18" t="s">
-        <v>133</v>
       </c>
       <c r="N18">
         <v>1</v>
       </c>
       <c r="O18" t="s">
+        <v>133</v>
+      </c>
+      <c r="P18" t="s">
         <v>134</v>
-      </c>
-      <c r="P18" t="s">
-        <v>135</v>
       </c>
       <c r="Q18">
         <v>31</v>
@@ -11504,7 +11517,7 @@
         <v>61</v>
       </c>
       <c r="S18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T18">
         <v>32</v>
@@ -11513,7 +11526,7 @@
         <v>62</v>
       </c>
       <c r="V18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W18">
         <v>180</v>
@@ -11522,7 +11535,7 @@
         <v>50</v>
       </c>
       <c r="Y18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z18">
         <v>31</v>
@@ -11531,7 +11544,7 @@
         <v>61</v>
       </c>
       <c r="AB18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC18">
         <v>32</v>
@@ -11543,16 +11556,16 @@
         <v>900</v>
       </c>
       <c r="AF18" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG18" t="s">
         <v>137</v>
       </c>
-      <c r="AG18" t="s">
+      <c r="AH18" t="s">
         <v>138</v>
       </c>
-      <c r="AH18" t="s">
+      <c r="AI18" t="s">
         <v>139</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>140</v>
       </c>
       <c r="AJ18">
         <v>10</v>
@@ -11561,7 +11574,7 @@
         <v>1.5</v>
       </c>
       <c r="AL18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AM18">
         <v>1.42</v>
@@ -11588,22 +11601,22 @@
         <v>120</v>
       </c>
       <c r="AU18" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV18" t="s">
         <v>142</v>
       </c>
-      <c r="AV18" t="s">
-        <v>143</v>
-      </c>
       <c r="AW18" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX18" t="s">
         <v>137</v>
       </c>
-      <c r="AX18" t="s">
+      <c r="AY18" t="s">
         <v>138</v>
       </c>
-      <c r="AY18" t="s">
+      <c r="AZ18" t="s">
         <v>139</v>
-      </c>
-      <c r="AZ18" t="s">
-        <v>140</v>
       </c>
       <c r="BA18">
         <v>10</v>
@@ -11612,7 +11625,7 @@
         <v>1.5</v>
       </c>
       <c r="BC18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BD18">
         <v>20</v>
@@ -11621,31 +11634,31 @@
         <v>1.5</v>
       </c>
       <c r="BF18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BG18">
         <v>1.42</v>
       </c>
       <c r="BH18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI18">
         <v>1.42</v>
       </c>
       <c r="BJ18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK18">
         <v>1.42</v>
       </c>
       <c r="BL18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BM18">
         <v>1.42</v>
       </c>
       <c r="BN18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BO18">
         <v>1.42</v>
@@ -11660,22 +11673,22 @@
         <v>120</v>
       </c>
       <c r="BS18" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT18" t="s">
         <v>142</v>
       </c>
-      <c r="BT18" t="s">
-        <v>143</v>
-      </c>
       <c r="BU18" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV18" t="s">
         <v>137</v>
       </c>
-      <c r="BV18" t="s">
+      <c r="BW18" t="s">
         <v>138</v>
       </c>
-      <c r="BW18" t="s">
+      <c r="BX18" t="s">
         <v>139</v>
-      </c>
-      <c r="BX18" t="s">
-        <v>140</v>
       </c>
       <c r="BY18">
         <v>10</v>
@@ -11684,13 +11697,13 @@
         <v>1.5</v>
       </c>
       <c r="CA18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CB18">
         <v>1.42</v>
       </c>
       <c r="CC18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CD18">
         <v>1.42</v>
@@ -11726,22 +11739,22 @@
         <v>120</v>
       </c>
       <c r="CO18" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP18" t="s">
         <v>142</v>
       </c>
-      <c r="CP18" t="s">
-        <v>143</v>
-      </c>
       <c r="CQ18" t="s">
+        <v>136</v>
+      </c>
+      <c r="CR18" t="s">
         <v>137</v>
       </c>
-      <c r="CR18" t="s">
+      <c r="CS18" t="s">
         <v>138</v>
       </c>
-      <c r="CS18" t="s">
+      <c r="CT18" t="s">
         <v>139</v>
-      </c>
-      <c r="CT18" t="s">
-        <v>140</v>
       </c>
       <c r="CU18">
         <v>10</v>
@@ -11750,19 +11763,19 @@
         <v>1.5</v>
       </c>
       <c r="CW18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CX18">
         <v>1.42</v>
       </c>
       <c r="CY18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CZ18">
         <v>1.42</v>
       </c>
       <c r="DA18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="DB18">
         <v>128</v>
@@ -11804,19 +11817,19 @@
         <v>120</v>
       </c>
       <c r="DO18" t="s">
+        <v>141</v>
+      </c>
+      <c r="DP18" t="s">
         <v>142</v>
       </c>
-      <c r="DP18" t="s">
-        <v>143</v>
-      </c>
       <c r="DQ18" t="s">
+        <v>144</v>
+      </c>
+      <c r="DR18" t="s">
         <v>145</v>
       </c>
-      <c r="DR18" t="s">
+      <c r="DS18" t="s">
         <v>146</v>
-      </c>
-      <c r="DS18" t="s">
-        <v>147</v>
       </c>
       <c r="DT18" t="b">
         <v>1</v>
@@ -11852,16 +11865,16 @@
         <v>1.5</v>
       </c>
       <c r="EE18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="EF18" t="s">
+        <v>144</v>
+      </c>
+      <c r="EG18" t="s">
         <v>145</v>
       </c>
-      <c r="EG18" t="s">
+      <c r="EH18" t="s">
         <v>146</v>
-      </c>
-      <c r="EH18" t="s">
-        <v>147</v>
       </c>
       <c r="EI18" t="b">
         <v>0</v>
@@ -11897,16 +11910,16 @@
         <v>1.5</v>
       </c>
       <c r="ET18" t="s">
+        <v>147</v>
+      </c>
+      <c r="EU18" t="s">
         <v>148</v>
       </c>
-      <c r="EU18" t="s">
+      <c r="EV18" t="s">
         <v>149</v>
       </c>
-      <c r="EV18" t="s">
+      <c r="EW18" t="s">
         <v>150</v>
-      </c>
-      <c r="EW18" t="s">
-        <v>151</v>
       </c>
       <c r="EX18">
         <v>9.9999999999999995E-7</v>
@@ -11921,13 +11934,13 @@
         <v>25</v>
       </c>
       <c r="FB18" t="s">
+        <v>148</v>
+      </c>
+      <c r="FC18" t="s">
         <v>149</v>
       </c>
-      <c r="FC18" t="s">
+      <c r="FD18" t="s">
         <v>150</v>
-      </c>
-      <c r="FD18" t="s">
-        <v>151</v>
       </c>
       <c r="FE18">
         <v>9.9999999999999995E-7</v>
@@ -11942,16 +11955,16 @@
         <v>25</v>
       </c>
       <c r="FI18" t="s">
+        <v>151</v>
+      </c>
+      <c r="FJ18" t="s">
+        <v>145</v>
+      </c>
+      <c r="FK18" t="s">
         <v>152</v>
       </c>
-      <c r="FJ18" t="s">
-        <v>146</v>
-      </c>
-      <c r="FK18" t="s">
+      <c r="FL18" t="s">
         <v>153</v>
-      </c>
-      <c r="FL18" t="s">
-        <v>154</v>
       </c>
       <c r="FM18">
         <v>200</v>
@@ -11978,7 +11991,7 @@
         <v>20</v>
       </c>
       <c r="FU18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="FV18">
         <v>532</v>
@@ -11999,19 +12012,19 @@
         <v>75</v>
       </c>
       <c r="GB18" t="s">
+        <v>155</v>
+      </c>
+      <c r="GC18" t="s">
         <v>156</v>
       </c>
-      <c r="GC18" t="s">
+      <c r="GD18" t="s">
+        <v>145</v>
+      </c>
+      <c r="GE18" t="s">
         <v>157</v>
       </c>
-      <c r="GD18" t="s">
-        <v>146</v>
-      </c>
-      <c r="GE18" t="s">
+      <c r="GF18" t="s">
         <v>158</v>
-      </c>
-      <c r="GF18" t="s">
-        <v>159</v>
       </c>
       <c r="GG18">
         <v>25</v>
@@ -12029,7 +12042,7 @@
         <v>250</v>
       </c>
       <c r="GL18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="GM18">
         <v>0.2</v>
@@ -12041,7 +12054,7 @@
         <v>25</v>
       </c>
       <c r="GP18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="GQ18">
         <v>0.1</v>
@@ -12056,19 +12069,19 @@
         <v>150</v>
       </c>
       <c r="GU18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="GV18">
         <v>35</v>
       </c>
       <c r="GW18" t="s">
+        <v>160</v>
+      </c>
+      <c r="GX18" t="s">
         <v>161</v>
       </c>
-      <c r="GX18" t="s">
+      <c r="GY18" t="s">
         <v>162</v>
-      </c>
-      <c r="GY18" t="s">
-        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -12091,5 +12104,6 @@
     <mergeCell ref="CQ1:DP1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tests/data/20250305_experiment_file.xlsx
+++ b/tests/data/20250305_experiment_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Desktop-PC\PycharmProjects\nomad-hysprint\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB17D7A1-13D6-433B-8F34-5988C92EB259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E75FB83-0B3C-49F2-86A2-0C062F70EC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
